--- a/uploads/xlsx/Timetable Spring-26 (1st-8th) 1.6 (Ramadan Timetable).xlsx
+++ b/uploads/xlsx/Timetable Spring-26 (1st-8th) 1.6 (Ramadan Timetable).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\zPythonStuff\Superior Academic Tool\uploads\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC93085-CAB9-449D-9D28-946683586931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054EF2E5-CAE8-4E19-8D45-C6D8A19ADBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4455" yWindow="2955" windowWidth="21600" windowHeight="14235" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Time Table" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="333">
   <si>
     <t>Week</t>
   </si>
@@ -226,19 +226,9 @@
 Mr. Muhammad Ilyas </t>
   </si>
   <si>
-    <t xml:space="preserve">Probability &amp; Statistics 
-BSAI-2D
-Ms. Sobia </t>
-  </si>
-  <si>
     <t xml:space="preserve">Linear Algebra 
 BSSE-4B
 Mr. Usama </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Probability &amp; Statistics 
-BSAI-2A
-Ms. Sobia </t>
   </si>
   <si>
     <t xml:space="preserve">Generative AI 
@@ -667,11 +657,6 @@
     <t xml:space="preserve">Linear Algebra 
 BSDS-4A
 Mr. Muhammad Hamza </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digital Marketing 
-BSSE-2D
-Mr. Raja Shahzaib </t>
   </si>
   <si>
     <t>Artificial Neural Networks
@@ -1248,26 +1233,6 @@
 Mr. Muhammad Ismail </t>
   </si>
   <si>
-    <t>Calculus &amp; Analytical Geometry 
-BSSE-2D
-Dr. Zoha Tariq</t>
-  </si>
-  <si>
-    <t>Calculus &amp; Analytical Geometry 
-BSAI-2C
-Dr. Zoha Tariq</t>
-  </si>
-  <si>
-    <t>Probability &amp; Statistics 
-BSSE-2C
-Dr. Zoha Tariq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calculus &amp; Analytical Geometry 
-BSSE-2E
-Dr. Zoha Tariq </t>
-  </si>
-  <si>
     <t xml:space="preserve">Application of Information &amp; Communication &amp; Technologies (Lab)
 BSSE-1A/BSDS-1A
 Ms. Momna Naseem </t>
@@ -1318,33 +1283,8 @@
 Ms. Salwa Batool </t>
   </si>
   <si>
-    <t xml:space="preserve">Programming Fundamentals (Thoery)
-BSSE-2D
-Ms. Salwa Batool </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programming Fundamentals 
-BSSE-2B
-Ms. Salwa Batool </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programming Fundamentals 
-BSSE-2E
-Ms. Salwa Batool </t>
-  </si>
-  <si>
     <t xml:space="preserve">Programming Fundamentals 
 BSSE-2C
-Mr. Umer Khalil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programming Fundamentals (Theory)
-BSDS-2A
-Mr. Umer Khalil </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programming Fundamentals 
-BSAI-2C
 Mr. Umer Khalil </t>
   </si>
   <si>
@@ -1383,16 +1323,6 @@
 Ms. Ayesha Aslam</t>
   </si>
   <si>
-    <t>Programming Fundamentals 
-BSAI-2D
-Ms. Ayesha Aslam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programming Fundamentals 
-BSAI-2E
-Ms. Ayesha Aslam </t>
-  </si>
-  <si>
     <t xml:space="preserve">Expository Writing 
 BSSE-2A
 Ms. Javaria Waleed </t>
@@ -1404,69 +1334,9 @@
   </si>
   <si>
     <t>Fahm e quran II
-BSSE-2A
-TBA
-(08:00 - 09:00)</t>
-  </si>
-  <si>
-    <t>Fahm e quran II
 BSDS-2A
 TBA
 (02:00 - 03:00)</t>
-  </si>
-  <si>
-    <t>Fahm e quran II
-BSAI-2A
-TBA
-(08:00 - 09:00)</t>
-  </si>
-  <si>
-    <t>Fahm e quran II
-BSSE-2B
-TBA
-(09:00 - 10:00)</t>
-  </si>
-  <si>
-    <t>Fahm e quran II
-BSSE-2C
-TBA
-(10:00 - 11:00)</t>
-  </si>
-  <si>
-    <t>Fahm e quran II
-BSSE-2D
-TBA
-(11:00 - 12:00)</t>
-  </si>
-  <si>
-    <t>Fahm e quran II
-BSSE-2E
-TBA
-(12:00 - 01:00)</t>
-  </si>
-  <si>
-    <t>Fahm e quran II
-BSAI-2B
-TBA
-(09:00 - 10:00)</t>
-  </si>
-  <si>
-    <t>Fahm e quran II
-BSAI-2C
-TBA
-(10:00 - 11:00)</t>
-  </si>
-  <si>
-    <t>Fahm e quran II
-BSAI-2D
-TBA
-(11:00 - 12:00)</t>
-  </si>
-  <si>
-    <t>Fahm e quran II
-BSAI-2E
-TBA
-(12:00 - 01:00)</t>
   </si>
   <si>
     <t>Online Classes</t>
@@ -1568,7 +1438,140 @@
     <t>12:00 - 02:00</t>
   </si>
   <si>
+    <t>Calculus &amp; Analytical Geometry 
+BSSE-2D
+Ms. Dilawaiz</t>
+  </si>
+  <si>
+    <t>Calculus &amp; Analytical Geometry 
+BSAI-2C
+Ms. Dilawaiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculus &amp; Analytical Geometry 
+BSSE-2E
+Ms. Dilawaiz </t>
+  </si>
+  <si>
+    <t>Probability &amp; Statistics 
+BSSE-2C
+Ms. Dilawaiz</t>
+  </si>
+  <si>
+    <t>Programming Fundamentals 
+BSSE-2E
+Ms. Ayesha Aslam</t>
+  </si>
+  <si>
+    <t>Programming Fundamentals 
+BSAI-2D
+Ms. Salwa Batool</t>
+  </si>
+  <si>
+    <t>Programming Fundamentals 
+BSSE-2B
+Mr. Umer Khalil</t>
+  </si>
+  <si>
+    <t>Programming Fundamentals (Theory)
+BSDS-2A
+Ms. Ayesha Aslam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programming Fundamentals 
+BSAI-2C
+Ms. Salwa Batool </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programming Fundamentals 
+BSAI-2E
+Ms. Salwa Batool </t>
+  </si>
+  <si>
+    <t>Probability &amp; Statistics 
+BSAI-2A
+Ms. Dilawaiz</t>
+  </si>
+  <si>
+    <t>Probability &amp; Statistics 
+BSAI-2D
+Mr. Muhammad Ismail</t>
+  </si>
+  <si>
+    <t>Digital Marketing 
+BSSE-2D
+Mr. Raja Shahzaib</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Programming Fundamentals (Thoery)
+BSSE-2D
+Mr. Umer Khalill</t>
+  </si>
+  <si>
+    <t>Fahm e quran II
+BSAI-2A
+Mr. M. Farooq
+(08:00 - 09:00)</t>
+  </si>
+  <si>
+    <t>Fahm e quran II
+BSAI-2B
+Mr. M. Farooq
+(09:00 - 10:00)</t>
+  </si>
+  <si>
+    <t>Fahm e quran II
+BSAI-2C
+Mr. M. Farooq
+(10:00 - 11:00)</t>
+  </si>
+  <si>
+    <t>Fahm e quran II
+BSAI-2D
+Mr. M. Farooq
+(11:00 - 12:00)</t>
+  </si>
+  <si>
+    <t>Fahm e quran II
+BSAI-2E
+Mr. M. Farooq
+(12:00 - 01:00)</t>
+  </si>
+  <si>
+    <t>Fahm e quran II
+BSSE-2E
+Mr. Muhammad Usman Sadiqi 
+(12:00 - 01:00)</t>
+  </si>
+  <si>
+    <t>Fahm e quran II
+BSSE-2D
+Mr. Muhammad Usman Sadiqi 
+(11:00 - 12:00)</t>
+  </si>
+  <si>
+    <t>Fahm e quran II
+BSSE-2C
+Mr. Muhammad Usman Sadiqi 
+(10:00 - 11:00)</t>
+  </si>
+  <si>
+    <t>Fahm e quran II
+BSSE-2B
+Mr. Muhammad Usman Sadiqi 
+(09:00 - 10:00)</t>
+  </si>
+  <si>
+    <t>Fahm e quran II
+BSSE-2A
+Mr. Muhammad Usman Sadiqi 
+(08:00 - 09:00)</t>
+  </si>
+  <si>
     <t>11:00 - 12:00</t>
+  </si>
+  <si>
+    <t>02:00 - 03:00</t>
   </si>
   <si>
     <t xml:space="preserve">Software Re-Engineering 
@@ -1750,7 +1753,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1961,8 +1964,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor rgb="FF93C47D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor rgb="FFEAD1DC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="157">
+  <borders count="156">
     <border>
       <left/>
       <right/>
@@ -2444,15 +2459,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color rgb="FF000000"/>
@@ -2800,19 +2806,6 @@
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
@@ -3810,21 +3803,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="379">
+  <cellXfs count="391">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="93" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="91" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="93" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="91" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="94" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3840,7 +3846,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3851,13 +3857,13 @@
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3866,7 +3872,7 @@
     <xf numFmtId="164" fontId="9" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="98" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3878,11 +3884,11 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="101" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="99" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3897,7 +3903,7 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3906,52 +3912,52 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="88" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3960,19 +3966,19 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="98" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3991,10 +3997,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="98" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="98" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4006,30 +4012,30 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4046,161 +4052,170 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="85" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="107" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="105" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="108" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="106" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="107" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="109" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="109" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="110" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="111" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="111" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="116" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="117" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="118" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="119" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="120" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="88" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="103" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="87" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="121" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="122" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="105" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="125" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="126" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="127" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="126" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="128" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="125" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="118" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="88" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="127" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="120" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="129" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="130" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="131" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="128" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="129" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="130" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="131" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="132" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="133" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="134" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="137" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="135" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="138" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="111" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="122" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="120" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="142" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="143" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="144" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4209,158 +4224,149 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="146" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="134" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="111" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="147" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="149" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="126" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="143" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="149" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="143" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="117" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="151" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="154" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="91" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="156" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="93" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="94" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="105" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="103" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="131" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="129" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="34" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="34" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="34" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="31" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="103" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="101" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="111" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="109" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="143" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="117" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="117" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="119" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="117" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4378,40 +4384,50 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="36" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="36" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4421,11 +4437,11 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4441,45 +4457,49 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="24" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="37" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="16" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="88" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -4490,7 +4510,7 @@
     <xf numFmtId="0" fontId="12" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="12" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4499,45 +4519,46 @@
     <xf numFmtId="0" fontId="12" fillId="13" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="88" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="119" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="28" borderId="117" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="121" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="36" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="89" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="119" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="36" borderId="88" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="88" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="87" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="119" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="117" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="115" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="111" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="109" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4563,143 +4584,150 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="134" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="137" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="138" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="135" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="133" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="137" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="138" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="135" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="106" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="110" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="116" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="142" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="108" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="98" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="87" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="87" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="128" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="126" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="154" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="155" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="143" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="35" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="98" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="35" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="119" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="18" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="119" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="117" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="141" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="143" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="12" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="36" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="95" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="93" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4949,10 +4977,10 @@
       <c r="D1" s="58"/>
       <c r="E1" s="58"/>
       <c r="F1" s="58"/>
-      <c r="G1" s="295"/>
-      <c r="H1" s="296"/>
-      <c r="I1" s="296"/>
-      <c r="J1" s="297"/>
+      <c r="G1" s="304"/>
+      <c r="H1" s="305"/>
+      <c r="I1" s="305"/>
+      <c r="J1" s="306"/>
       <c r="K1" s="59"/>
       <c r="L1" s="60"/>
       <c r="M1" s="60"/>
@@ -4973,20 +5001,20 @@
       <c r="AB1" s="61"/>
     </row>
     <row r="2" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A2" s="301" t="s">
-        <v>215</v>
-      </c>
-      <c r="B2" s="296"/>
-      <c r="C2" s="296"/>
-      <c r="D2" s="296"/>
-      <c r="E2" s="297"/>
+      <c r="A2" s="310" t="s">
+        <v>212</v>
+      </c>
+      <c r="B2" s="305"/>
+      <c r="C2" s="305"/>
+      <c r="D2" s="305"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="298"/>
-      <c r="H2" s="299"/>
-      <c r="I2" s="299"/>
-      <c r="J2" s="300"/>
+      <c r="G2" s="307"/>
+      <c r="H2" s="308"/>
+      <c r="I2" s="308"/>
+      <c r="J2" s="309"/>
       <c r="K2" s="63"/>
       <c r="L2" s="60"/>
       <c r="M2" s="60"/>
@@ -5007,18 +5035,18 @@
       <c r="AB2" s="61"/>
     </row>
     <row r="3" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A3" s="302"/>
-      <c r="B3" s="303"/>
-      <c r="C3" s="303"/>
-      <c r="D3" s="303"/>
-      <c r="E3" s="304"/>
+      <c r="A3" s="311"/>
+      <c r="B3" s="312"/>
+      <c r="C3" s="312"/>
+      <c r="D3" s="312"/>
+      <c r="E3" s="313"/>
       <c r="F3" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="308"/>
+      <c r="G3" s="317"/>
       <c r="H3" s="227"/>
       <c r="I3" s="227"/>
-      <c r="J3" s="273"/>
+      <c r="J3" s="281"/>
       <c r="K3" s="64"/>
       <c r="L3" s="60"/>
       <c r="M3" s="60"/>
@@ -5039,18 +5067,18 @@
       <c r="AB3" s="61"/>
     </row>
     <row r="4" spans="1:28" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A4" s="305"/>
-      <c r="B4" s="306"/>
-      <c r="C4" s="306"/>
-      <c r="D4" s="306"/>
-      <c r="E4" s="307"/>
+      <c r="A4" s="314"/>
+      <c r="B4" s="315"/>
+      <c r="C4" s="315"/>
+      <c r="D4" s="315"/>
+      <c r="E4" s="316"/>
       <c r="F4" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="309"/>
-      <c r="H4" s="310"/>
-      <c r="I4" s="310"/>
-      <c r="J4" s="311"/>
+      <c r="G4" s="318"/>
+      <c r="H4" s="319"/>
+      <c r="I4" s="319"/>
+      <c r="J4" s="320"/>
       <c r="K4" s="65"/>
       <c r="L4" s="60"/>
       <c r="M4" s="60"/>
@@ -5071,34 +5099,34 @@
       <c r="AB4" s="61"/>
     </row>
     <row r="5" spans="1:28" ht="16.5" thickBot="1">
-      <c r="A5" s="130"/>
-      <c r="B5" s="131" t="s">
+      <c r="A5" s="133"/>
+      <c r="B5" s="134" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="48"/>
-      <c r="D5" s="132" t="s">
-        <v>299</v>
-      </c>
-      <c r="E5" s="133" t="s">
-        <v>300</v>
-      </c>
-      <c r="F5" s="133" t="s">
-        <v>301</v>
-      </c>
-      <c r="G5" s="133" t="s">
-        <v>302</v>
-      </c>
-      <c r="H5" s="134" t="s">
-        <v>303</v>
-      </c>
-      <c r="I5" s="134" t="s">
-        <v>304</v>
-      </c>
-      <c r="J5" s="134" t="s">
-        <v>305</v>
-      </c>
-      <c r="K5" s="135" t="s">
-        <v>306</v>
+      <c r="D5" s="135" t="s">
+        <v>275</v>
+      </c>
+      <c r="E5" s="136" t="s">
+        <v>276</v>
+      </c>
+      <c r="F5" s="136" t="s">
+        <v>277</v>
+      </c>
+      <c r="G5" s="136" t="s">
+        <v>278</v>
+      </c>
+      <c r="H5" s="137" t="s">
+        <v>279</v>
+      </c>
+      <c r="I5" s="137" t="s">
+        <v>280</v>
+      </c>
+      <c r="J5" s="137" t="s">
+        <v>281</v>
+      </c>
+      <c r="K5" s="138" t="s">
+        <v>282</v>
       </c>
       <c r="L5" s="60"/>
       <c r="M5" s="60"/>
@@ -5119,27 +5147,27 @@
       <c r="AB5" s="61"/>
     </row>
     <row r="6" spans="1:28" ht="48" customHeight="1" thickBot="1">
-      <c r="A6" s="324" t="s">
+      <c r="A6" s="333" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="137" t="s">
+      <c r="B6" s="140" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="312" t="s">
+      <c r="C6" s="321" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="318" t="s">
+      <c r="D6" s="327" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="319"/>
-      <c r="F6" s="319"/>
-      <c r="G6" s="320"/>
-      <c r="H6" s="316" t="s">
+      <c r="E6" s="328"/>
+      <c r="F6" s="328"/>
+      <c r="G6" s="329"/>
+      <c r="H6" s="325" t="s">
         <v>41</v>
       </c>
-      <c r="I6" s="317"/>
-      <c r="J6" s="138"/>
-      <c r="K6" s="139"/>
+      <c r="I6" s="326"/>
+      <c r="J6" s="141"/>
+      <c r="K6" s="142"/>
       <c r="L6" s="60"/>
       <c r="M6" s="60"/>
       <c r="N6" s="60"/>
@@ -5159,23 +5187,23 @@
       <c r="AB6" s="61"/>
     </row>
     <row r="7" spans="1:28" ht="65.25" customHeight="1" thickBot="1">
-      <c r="A7" s="325"/>
+      <c r="A7" s="334"/>
       <c r="B7" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="313"/>
-      <c r="D7" s="263" t="s">
+      <c r="C7" s="322"/>
+      <c r="D7" s="270" t="s">
         <v>4</v>
       </c>
       <c r="E7" s="187"/>
       <c r="F7" s="187"/>
       <c r="G7" s="180"/>
       <c r="H7" s="209" t="s">
-        <v>255</v>
+        <v>298</v>
       </c>
       <c r="I7" s="180"/>
       <c r="J7" s="55"/>
-      <c r="K7" s="140"/>
+      <c r="K7" s="143"/>
       <c r="L7" s="60"/>
       <c r="M7" s="60"/>
       <c r="N7" s="60"/>
@@ -5195,27 +5223,27 @@
       <c r="AB7" s="61"/>
     </row>
     <row r="8" spans="1:28" ht="46.5" customHeight="1">
-      <c r="A8" s="325"/>
+      <c r="A8" s="334"/>
       <c r="B8" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="314" t="s">
+      <c r="C8" s="323" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="268" t="s">
-        <v>280</v>
+      <c r="D8" s="275" t="s">
+        <v>268</v>
       </c>
       <c r="E8" s="187"/>
       <c r="F8" s="199" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G8" s="180"/>
       <c r="H8" s="182" t="s">
         <v>45</v>
       </c>
       <c r="I8" s="183"/>
-      <c r="J8" s="292"/>
-      <c r="K8" s="293"/>
+      <c r="J8" s="285"/>
+      <c r="K8" s="302"/>
       <c r="L8" s="60"/>
       <c r="M8" s="60"/>
       <c r="N8" s="60"/>
@@ -5235,12 +5263,12 @@
       <c r="AB8" s="61"/>
     </row>
     <row r="9" spans="1:28" ht="60" customHeight="1">
-      <c r="A9" s="325"/>
+      <c r="A9" s="334"/>
       <c r="B9" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="315"/>
-      <c r="D9" s="263" t="s">
+      <c r="C9" s="324"/>
+      <c r="D9" s="270" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="180"/>
@@ -5253,7 +5281,7 @@
       </c>
       <c r="I9" s="180"/>
       <c r="J9" s="71"/>
-      <c r="K9" s="141"/>
+      <c r="K9" s="144"/>
       <c r="L9" s="60"/>
       <c r="M9" s="60"/>
       <c r="N9" s="60"/>
@@ -5273,25 +5301,25 @@
       <c r="AB9" s="61"/>
     </row>
     <row r="10" spans="1:28" ht="61.5" customHeight="1" thickBot="1">
-      <c r="A10" s="325"/>
+      <c r="A10" s="334"/>
       <c r="B10" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="315"/>
-      <c r="D10" s="268" t="s">
+      <c r="C10" s="324"/>
+      <c r="D10" s="275" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="180"/>
       <c r="F10" s="179" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="G10" s="180"/>
       <c r="H10" s="181" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I10" s="180"/>
       <c r="J10" s="109"/>
-      <c r="K10" s="141"/>
+      <c r="K10" s="144"/>
       <c r="L10" s="60"/>
       <c r="M10" s="60"/>
       <c r="N10" s="60"/>
@@ -5311,11 +5339,11 @@
       <c r="AB10" s="61"/>
     </row>
     <row r="11" spans="1:28" ht="48" customHeight="1">
-      <c r="A11" s="325"/>
+      <c r="A11" s="334"/>
       <c r="B11" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="314" t="s">
+      <c r="C11" s="323" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="190" t="s">
@@ -5323,17 +5351,17 @@
       </c>
       <c r="E11" s="180"/>
       <c r="F11" s="199" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="G11" s="180"/>
-      <c r="H11" s="142" t="s">
+      <c r="H11" s="145" t="s">
         <v>18</v>
       </c>
       <c r="I11" s="179" t="s">
         <v>19</v>
       </c>
       <c r="J11" s="180"/>
-      <c r="K11" s="143"/>
+      <c r="K11" s="146"/>
       <c r="L11" s="60"/>
       <c r="M11" s="60"/>
       <c r="N11" s="60"/>
@@ -5353,11 +5381,11 @@
       <c r="AB11" s="61"/>
     </row>
     <row r="12" spans="1:28" ht="60" customHeight="1">
-      <c r="A12" s="325"/>
+      <c r="A12" s="334"/>
       <c r="B12" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="315"/>
+      <c r="C12" s="324"/>
       <c r="D12" s="207" t="s">
         <v>21</v>
       </c>
@@ -5367,7 +5395,7 @@
       </c>
       <c r="G12" s="180"/>
       <c r="H12" s="195" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I12" s="180"/>
       <c r="J12" s="202"/>
@@ -5391,13 +5419,13 @@
       <c r="AB12" s="61"/>
     </row>
     <row r="13" spans="1:28" ht="87" customHeight="1">
-      <c r="A13" s="325"/>
+      <c r="A13" s="334"/>
       <c r="B13" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="315"/>
+      <c r="C13" s="324"/>
       <c r="D13" s="190" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E13" s="180"/>
       <c r="F13" s="179" t="s">
@@ -5405,7 +5433,7 @@
       </c>
       <c r="G13" s="180"/>
       <c r="H13" s="172" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="I13" s="173"/>
       <c r="J13" s="174"/>
@@ -5429,27 +5457,27 @@
       <c r="AB13" s="61"/>
     </row>
     <row r="14" spans="1:28" ht="51.75" customHeight="1">
-      <c r="A14" s="325"/>
+      <c r="A14" s="334"/>
       <c r="B14" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="315"/>
+      <c r="C14" s="324"/>
       <c r="D14" s="196" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="197"/>
       <c r="F14" s="198" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="G14" s="187"/>
-      <c r="H14" s="356" t="s">
+      <c r="H14" s="243" t="s">
         <v>27</v>
       </c>
-      <c r="I14" s="356"/>
+      <c r="I14" s="243"/>
       <c r="J14" s="182" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="294"/>
+      <c r="K14" s="303"/>
       <c r="L14" s="60"/>
       <c r="M14" s="60"/>
       <c r="N14" s="60"/>
@@ -5469,21 +5497,21 @@
       <c r="AB14" s="61"/>
     </row>
     <row r="15" spans="1:28" ht="53.25" customHeight="1">
-      <c r="A15" s="325"/>
+      <c r="A15" s="334"/>
       <c r="B15" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="315"/>
-      <c r="D15" s="243" t="s">
-        <v>272</v>
-      </c>
-      <c r="E15" s="244"/>
+      <c r="C15" s="324"/>
+      <c r="D15" s="249" t="s">
+        <v>262</v>
+      </c>
+      <c r="E15" s="250"/>
       <c r="F15" s="199" t="s">
-        <v>256</v>
+        <v>299</v>
       </c>
       <c r="G15" s="180"/>
       <c r="H15" s="200" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="I15" s="201"/>
       <c r="J15" s="202"/>
@@ -5507,11 +5535,11 @@
       <c r="AB15" s="61"/>
     </row>
     <row r="16" spans="1:28" ht="57.75" customHeight="1">
-      <c r="A16" s="325"/>
+      <c r="A16" s="334"/>
       <c r="B16" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="315"/>
+      <c r="C16" s="324"/>
       <c r="D16" s="204" t="s">
         <v>4</v>
       </c>
@@ -5545,13 +5573,13 @@
       <c r="AB16" s="61"/>
     </row>
     <row r="17" spans="1:28" ht="71.25" customHeight="1">
-      <c r="A17" s="325"/>
+      <c r="A17" s="334"/>
       <c r="B17" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="315"/>
+      <c r="C17" s="324"/>
       <c r="D17" s="207" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="E17" s="180"/>
       <c r="F17" s="179" t="s">
@@ -5559,7 +5587,7 @@
       </c>
       <c r="G17" s="180"/>
       <c r="H17" s="199" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="I17" s="180"/>
       <c r="J17" s="179" t="s">
@@ -5585,19 +5613,19 @@
       <c r="AB17" s="61"/>
     </row>
     <row r="18" spans="1:28" ht="64.5" customHeight="1">
-      <c r="A18" s="325"/>
+      <c r="A18" s="334"/>
       <c r="B18" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="315"/>
+      <c r="C18" s="324"/>
       <c r="D18" s="207" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="E18" s="180"/>
-      <c r="F18" s="209" t="s">
-        <v>269</v>
-      </c>
-      <c r="G18" s="270"/>
+      <c r="F18" s="277" t="s">
+        <v>310</v>
+      </c>
+      <c r="G18" s="278"/>
       <c r="H18" s="209" t="s">
         <v>37</v>
       </c>
@@ -5625,17 +5653,17 @@
       <c r="AB18" s="61"/>
     </row>
     <row r="19" spans="1:28" ht="60.75" customHeight="1">
-      <c r="A19" s="325"/>
+      <c r="A19" s="334"/>
       <c r="B19" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="315"/>
+      <c r="C19" s="324"/>
       <c r="D19" s="207" t="s">
         <v>40</v>
       </c>
       <c r="E19" s="180"/>
       <c r="F19" s="209" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="G19" s="211"/>
       <c r="H19" s="179" t="s">
@@ -5663,21 +5691,21 @@
       <c r="AB19" s="61"/>
     </row>
     <row r="20" spans="1:28" ht="49.5" customHeight="1" thickBot="1">
-      <c r="A20" s="326"/>
-      <c r="B20" s="144" t="s">
+      <c r="A20" s="335"/>
+      <c r="B20" s="147" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="327"/>
+      <c r="C20" s="336"/>
       <c r="D20" s="212" t="s">
         <v>44</v>
       </c>
       <c r="E20" s="213"/>
       <c r="F20" s="212" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G20" s="214"/>
       <c r="H20" s="215" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="I20" s="213"/>
       <c r="J20" s="104"/>
@@ -5702,10 +5730,10 @@
     </row>
     <row r="21" spans="1:28" ht="15.75" customHeight="1" thickBot="1">
       <c r="A21" s="91"/>
-      <c r="B21" s="328" t="s">
+      <c r="B21" s="337" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="329"/>
+      <c r="C21" s="338"/>
       <c r="D21" s="92"/>
       <c r="E21" s="106"/>
       <c r="F21" s="106"/>
@@ -5713,7 +5741,7 @@
       <c r="H21" s="54"/>
       <c r="I21" s="54"/>
       <c r="J21" s="54"/>
-      <c r="K21" s="136"/>
+      <c r="K21" s="139"/>
       <c r="L21" s="60"/>
       <c r="M21" s="60"/>
       <c r="N21" s="60"/>
@@ -5733,36 +5761,36 @@
       <c r="AB21" s="61"/>
     </row>
     <row r="22" spans="1:28" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A22" s="321" t="s">
+      <c r="A22" s="330" t="s">
         <v>46</v>
       </c>
       <c r="B22" s="33" t="s">
         <v>47</v>
       </c>
       <c r="C22" s="34"/>
-      <c r="D22" s="132" t="s">
-        <v>299</v>
-      </c>
-      <c r="E22" s="133" t="s">
-        <v>300</v>
-      </c>
-      <c r="F22" s="133" t="s">
-        <v>301</v>
-      </c>
-      <c r="G22" s="133" t="s">
-        <v>302</v>
-      </c>
-      <c r="H22" s="134" t="s">
-        <v>303</v>
-      </c>
-      <c r="I22" s="134" t="s">
-        <v>304</v>
-      </c>
-      <c r="J22" s="134" t="s">
-        <v>305</v>
-      </c>
-      <c r="K22" s="135" t="s">
-        <v>306</v>
+      <c r="D22" s="135" t="s">
+        <v>275</v>
+      </c>
+      <c r="E22" s="136" t="s">
+        <v>276</v>
+      </c>
+      <c r="F22" s="136" t="s">
+        <v>277</v>
+      </c>
+      <c r="G22" s="136" t="s">
+        <v>278</v>
+      </c>
+      <c r="H22" s="137" t="s">
+        <v>279</v>
+      </c>
+      <c r="I22" s="137" t="s">
+        <v>280</v>
+      </c>
+      <c r="J22" s="137" t="s">
+        <v>281</v>
+      </c>
+      <c r="K22" s="138" t="s">
+        <v>282</v>
       </c>
       <c r="L22" s="60"/>
       <c r="M22" s="60"/>
@@ -5783,11 +5811,11 @@
       <c r="AB22" s="61"/>
     </row>
     <row r="23" spans="1:28" ht="42" customHeight="1">
-      <c r="A23" s="322"/>
+      <c r="A23" s="331"/>
       <c r="B23" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="321" t="s">
+      <c r="C23" s="330" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="222" t="s">
@@ -5797,7 +5825,7 @@
       <c r="F23" s="223"/>
       <c r="G23" s="224"/>
       <c r="H23" s="225" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I23" s="224"/>
       <c r="J23" s="66"/>
@@ -5821,11 +5849,11 @@
       <c r="AB23" s="61"/>
     </row>
     <row r="24" spans="1:28" ht="49.5" customHeight="1" thickBot="1">
-      <c r="A24" s="322"/>
+      <c r="A24" s="331"/>
       <c r="B24" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="323"/>
+      <c r="C24" s="332"/>
       <c r="D24" s="226" t="s">
         <v>4</v>
       </c>
@@ -5857,23 +5885,23 @@
       <c r="AB24" s="61"/>
     </row>
     <row r="25" spans="1:28" ht="51" customHeight="1">
-      <c r="A25" s="322"/>
+      <c r="A25" s="331"/>
       <c r="B25" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="321" t="s">
+      <c r="C25" s="330" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="232" t="s">
-        <v>281</v>
-      </c>
-      <c r="E25" s="233"/>
-      <c r="F25" s="231" t="s">
+      <c r="D25" s="233" t="s">
+        <v>269</v>
+      </c>
+      <c r="E25" s="234"/>
+      <c r="F25" s="241" t="s">
+        <v>246</v>
+      </c>
+      <c r="G25" s="242"/>
+      <c r="H25" s="218" t="s">
         <v>51</v>
-      </c>
-      <c r="G25" s="228"/>
-      <c r="H25" s="218" t="s">
-        <v>52</v>
       </c>
       <c r="I25" s="228"/>
       <c r="J25" s="218"/>
@@ -5897,23 +5925,23 @@
       <c r="AB25" s="61"/>
     </row>
     <row r="26" spans="1:28" ht="52.5" customHeight="1">
-      <c r="A26" s="322"/>
+      <c r="A26" s="331"/>
       <c r="B26" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="322"/>
-      <c r="D26" s="234" t="s">
+      <c r="C26" s="331"/>
+      <c r="D26" s="235" t="s">
+        <v>308</v>
+      </c>
+      <c r="E26" s="236"/>
+      <c r="F26" s="237" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" s="238"/>
+      <c r="H26" s="239" t="s">
         <v>53</v>
       </c>
-      <c r="E26" s="228"/>
-      <c r="F26" s="235" t="s">
-        <v>54</v>
-      </c>
-      <c r="G26" s="236"/>
-      <c r="H26" s="237" t="s">
-        <v>55</v>
-      </c>
-      <c r="I26" s="238"/>
+      <c r="I26" s="240"/>
       <c r="J26" s="218"/>
       <c r="K26" s="219"/>
       <c r="L26" s="60"/>
@@ -5935,21 +5963,21 @@
       <c r="AB26" s="61"/>
     </row>
     <row r="27" spans="1:28" ht="54.75" customHeight="1" thickBot="1">
-      <c r="A27" s="322"/>
+      <c r="A27" s="331"/>
       <c r="B27" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C27" s="323"/>
-      <c r="D27" s="276" t="s">
-        <v>254</v>
-      </c>
-      <c r="E27" s="273"/>
-      <c r="F27" s="277" t="s">
-        <v>57</v>
-      </c>
-      <c r="G27" s="173"/>
+      <c r="C27" s="332"/>
+      <c r="D27" s="284" t="s">
+        <v>251</v>
+      </c>
+      <c r="E27" s="281"/>
+      <c r="F27" s="285" t="s">
+        <v>55</v>
+      </c>
+      <c r="G27" s="217"/>
       <c r="H27" s="218" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I27" s="228"/>
       <c r="J27" s="218"/>
@@ -5973,25 +6001,25 @@
       <c r="AB27" s="61"/>
     </row>
     <row r="28" spans="1:28" ht="69" customHeight="1">
-      <c r="A28" s="322"/>
+      <c r="A28" s="331"/>
       <c r="B28" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="330" t="s">
+      <c r="C28" s="339" t="s">
         <v>16</v>
       </c>
       <c r="D28" s="176" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="E28" s="177"/>
-      <c r="F28" s="278" t="s">
-        <v>270</v>
+      <c r="F28" s="286" t="s">
+        <v>304</v>
       </c>
       <c r="G28" s="228"/>
-      <c r="H28" s="274" t="s">
-        <v>66</v>
-      </c>
-      <c r="I28" s="275"/>
+      <c r="H28" s="282" t="s">
+        <v>64</v>
+      </c>
+      <c r="I28" s="283"/>
       <c r="J28" s="76"/>
       <c r="K28" s="72"/>
       <c r="L28" s="60"/>
@@ -6013,25 +6041,25 @@
       <c r="AB28" s="61"/>
     </row>
     <row r="29" spans="1:28" ht="54" customHeight="1">
-      <c r="A29" s="322"/>
+      <c r="A29" s="331"/>
       <c r="B29" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="331"/>
+      <c r="C29" s="340"/>
       <c r="D29" s="220" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E29" s="221"/>
-      <c r="F29" s="279" t="s">
-        <v>278</v>
+      <c r="F29" s="287" t="s">
+        <v>266</v>
       </c>
       <c r="G29" s="228"/>
       <c r="H29" s="216" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I29" s="217"/>
       <c r="J29" s="218" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K29" s="219"/>
       <c r="L29" s="60"/>
@@ -6053,23 +6081,23 @@
       <c r="AB29" s="61"/>
     </row>
     <row r="30" spans="1:28" ht="63">
-      <c r="A30" s="322"/>
+      <c r="A30" s="331"/>
       <c r="B30" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="331"/>
-      <c r="D30" s="262" t="s">
-        <v>61</v>
+      <c r="C30" s="340"/>
+      <c r="D30" s="269" t="s">
+        <v>59</v>
       </c>
       <c r="E30" s="228"/>
       <c r="F30" s="50" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="G30" s="110" t="s">
-        <v>311</v>
-      </c>
-      <c r="H30" s="253" t="s">
-        <v>258</v>
+        <v>287</v>
+      </c>
+      <c r="H30" s="259" t="s">
+        <v>300</v>
       </c>
       <c r="I30" s="228"/>
       <c r="J30" s="73"/>
@@ -6093,24 +6121,24 @@
       <c r="AB30" s="61"/>
     </row>
     <row r="31" spans="1:28" ht="62.25" customHeight="1">
-      <c r="A31" s="322"/>
+      <c r="A31" s="331"/>
       <c r="B31" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="331"/>
-      <c r="D31" s="262" t="s">
-        <v>62</v>
+      <c r="C31" s="340"/>
+      <c r="D31" s="269" t="s">
+        <v>60</v>
       </c>
       <c r="E31" s="228"/>
-      <c r="F31" s="271" t="s">
-        <v>63</v>
+      <c r="F31" s="279" t="s">
+        <v>61</v>
       </c>
       <c r="G31" s="173"/>
       <c r="H31" s="76"/>
-      <c r="I31" s="272" t="s">
-        <v>64</v>
-      </c>
-      <c r="J31" s="238"/>
+      <c r="I31" s="280" t="s">
+        <v>62</v>
+      </c>
+      <c r="J31" s="240"/>
       <c r="K31" s="77"/>
       <c r="L31" s="60"/>
       <c r="M31" s="60"/>
@@ -6131,25 +6159,25 @@
       <c r="AB31" s="61"/>
     </row>
     <row r="32" spans="1:28" ht="66.75" customHeight="1">
-      <c r="A32" s="322"/>
+      <c r="A32" s="331"/>
       <c r="B32" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="C32" s="331"/>
-      <c r="D32" s="262" t="s">
-        <v>65</v>
-      </c>
-      <c r="E32" s="273"/>
+      <c r="C32" s="340"/>
+      <c r="D32" s="269" t="s">
+        <v>63</v>
+      </c>
+      <c r="E32" s="281"/>
       <c r="F32" s="188" t="s">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="G32" s="189"/>
       <c r="H32" s="207" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I32" s="228"/>
-      <c r="J32" s="254" t="s">
-        <v>68</v>
+      <c r="J32" s="260" t="s">
+        <v>66</v>
       </c>
       <c r="K32" s="219"/>
       <c r="L32" s="60"/>
@@ -6171,25 +6199,25 @@
       <c r="AB32" s="61"/>
     </row>
     <row r="33" spans="1:28" ht="60.75" customHeight="1">
-      <c r="A33" s="322"/>
+      <c r="A33" s="331"/>
       <c r="B33" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="331"/>
-      <c r="D33" s="245" t="s">
-        <v>69</v>
+      <c r="C33" s="340"/>
+      <c r="D33" s="251" t="s">
+        <v>67</v>
       </c>
       <c r="E33" s="228"/>
-      <c r="F33" s="249" t="s">
+      <c r="F33" s="255" t="s">
         <v>4</v>
       </c>
       <c r="G33" s="201"/>
-      <c r="H33" s="246" t="s">
+      <c r="H33" s="252" t="s">
         <v>4</v>
       </c>
       <c r="I33" s="228"/>
-      <c r="J33" s="247"/>
-      <c r="K33" s="248"/>
+      <c r="J33" s="253"/>
+      <c r="K33" s="254"/>
       <c r="L33" s="60"/>
       <c r="M33" s="60"/>
       <c r="N33" s="60"/>
@@ -6209,25 +6237,25 @@
       <c r="AB33" s="61"/>
     </row>
     <row r="34" spans="1:28" ht="64.5" customHeight="1">
-      <c r="A34" s="322"/>
+      <c r="A34" s="331"/>
       <c r="B34" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="C34" s="331"/>
+      <c r="C34" s="340"/>
       <c r="D34" s="176" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="E34" s="177"/>
       <c r="F34" s="218" t="s">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="G34" s="228"/>
-      <c r="H34" s="241" t="s">
-        <v>70</v>
-      </c>
-      <c r="I34" s="236"/>
+      <c r="H34" s="246" t="s">
+        <v>68</v>
+      </c>
+      <c r="I34" s="247"/>
       <c r="J34" s="172"/>
-      <c r="K34" s="242"/>
+      <c r="K34" s="248"/>
       <c r="L34" s="60"/>
       <c r="M34" s="60"/>
       <c r="N34" s="60"/>
@@ -6247,25 +6275,25 @@
       <c r="AB34" s="61"/>
     </row>
     <row r="35" spans="1:28" ht="54.75" customHeight="1">
-      <c r="A35" s="322"/>
+      <c r="A35" s="331"/>
       <c r="B35" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="332"/>
-      <c r="D35" s="253" t="s">
-        <v>224</v>
+      <c r="C35" s="341"/>
+      <c r="D35" s="259" t="s">
+        <v>221</v>
       </c>
       <c r="E35" s="228"/>
-      <c r="F35" s="250" t="s">
-        <v>327</v>
+      <c r="F35" s="256" t="s">
+        <v>328</v>
       </c>
       <c r="G35" s="206"/>
       <c r="H35" s="218" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I35" s="228"/>
-      <c r="J35" s="251"/>
-      <c r="K35" s="242"/>
+      <c r="J35" s="257"/>
+      <c r="K35" s="248"/>
       <c r="L35" s="60"/>
       <c r="M35" s="60"/>
       <c r="N35" s="60"/>
@@ -6285,25 +6313,25 @@
       <c r="AB35" s="61"/>
     </row>
     <row r="36" spans="1:28" ht="49.5">
-      <c r="A36" s="322"/>
+      <c r="A36" s="331"/>
       <c r="B36" s="35" t="s">
         <v>39</v>
       </c>
       <c r="C36" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="D36" s="254" t="s">
-        <v>72</v>
+      <c r="D36" s="260" t="s">
+        <v>70</v>
       </c>
       <c r="E36" s="228"/>
-      <c r="F36" s="245" t="s">
+      <c r="F36" s="251" t="s">
         <v>36</v>
       </c>
-      <c r="G36" s="255"/>
-      <c r="H36" s="256" t="s">
-        <v>273</v>
-      </c>
-      <c r="I36" s="230"/>
+      <c r="G36" s="261"/>
+      <c r="H36" s="262" t="s">
+        <v>305</v>
+      </c>
+      <c r="I36" s="263"/>
       <c r="J36" s="55"/>
       <c r="K36" s="74"/>
       <c r="L36" s="60"/>
@@ -6324,24 +6352,24 @@
       <c r="AA36" s="61"/>
       <c r="AB36" s="61"/>
     </row>
-    <row r="37" spans="1:28" ht="54" thickBot="1">
-      <c r="A37" s="323"/>
+    <row r="37" spans="1:28" ht="53.25" thickBot="1">
+      <c r="A37" s="332"/>
       <c r="B37" s="38" t="s">
         <v>43</v>
       </c>
       <c r="C37" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="D37" s="257" t="s">
-        <v>73</v>
-      </c>
-      <c r="E37" s="258"/>
-      <c r="F37" s="259" t="s">
-        <v>74</v>
-      </c>
-      <c r="G37" s="260"/>
-      <c r="H37" s="261" t="s">
-        <v>239</v>
+      <c r="D37" s="264" t="s">
+        <v>71</v>
+      </c>
+      <c r="E37" s="265"/>
+      <c r="F37" s="266" t="s">
+        <v>72</v>
+      </c>
+      <c r="G37" s="267"/>
+      <c r="H37" s="268" t="s">
+        <v>236</v>
       </c>
       <c r="I37" s="228"/>
       <c r="J37" s="78"/>
@@ -6366,10 +6394,10 @@
     </row>
     <row r="38" spans="1:28" ht="15.75" customHeight="1" thickBot="1">
       <c r="A38" s="40"/>
-      <c r="B38" s="328" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" s="329"/>
+      <c r="B38" s="337" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="338"/>
       <c r="D38" s="92"/>
       <c r="E38" s="106"/>
       <c r="F38" s="106"/>
@@ -6397,36 +6425,36 @@
       <c r="AB38" s="61"/>
     </row>
     <row r="39" spans="1:28" ht="22.5" customHeight="1" thickBot="1">
-      <c r="A39" s="324" t="s">
-        <v>75</v>
+      <c r="A39" s="333" t="s">
+        <v>73</v>
       </c>
       <c r="B39" s="114" t="s">
         <v>47</v>
       </c>
       <c r="C39" s="94"/>
-      <c r="D39" s="166" t="s">
-        <v>299</v>
+      <c r="D39" s="165" t="s">
+        <v>275</v>
       </c>
       <c r="E39" s="95" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="F39" s="95" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="G39" s="95" t="s">
-        <v>302</v>
-      </c>
-      <c r="H39" s="167" t="s">
-        <v>303</v>
-      </c>
-      <c r="I39" s="167" t="s">
-        <v>304</v>
-      </c>
-      <c r="J39" s="167" t="s">
-        <v>305</v>
-      </c>
-      <c r="K39" s="168" t="s">
-        <v>306</v>
+        <v>278</v>
+      </c>
+      <c r="H39" s="166" t="s">
+        <v>279</v>
+      </c>
+      <c r="I39" s="166" t="s">
+        <v>280</v>
+      </c>
+      <c r="J39" s="166" t="s">
+        <v>281</v>
+      </c>
+      <c r="K39" s="167" t="s">
+        <v>282</v>
       </c>
       <c r="L39" s="60"/>
       <c r="M39" s="60"/>
@@ -6447,11 +6475,11 @@
       <c r="AB39" s="61"/>
     </row>
     <row r="40" spans="1:28" ht="51.75" customHeight="1">
-      <c r="A40" s="325"/>
+      <c r="A40" s="334"/>
       <c r="B40" s="49" t="s">
-        <v>298</v>
-      </c>
-      <c r="C40" s="314" t="s">
+        <v>274</v>
+      </c>
+      <c r="C40" s="323" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="222" t="s">
@@ -6460,8 +6488,8 @@
       <c r="E40" s="223"/>
       <c r="F40" s="223"/>
       <c r="G40" s="224"/>
-      <c r="H40" s="252" t="s">
-        <v>257</v>
+      <c r="H40" s="258" t="s">
+        <v>301</v>
       </c>
       <c r="I40" s="224"/>
       <c r="J40" s="66"/>
@@ -6485,23 +6513,23 @@
       <c r="AB40" s="61"/>
     </row>
     <row r="41" spans="1:28" ht="52.5" customHeight="1" thickBot="1">
-      <c r="A41" s="325"/>
+      <c r="A41" s="334"/>
       <c r="B41" s="49" t="s">
-        <v>76</v>
-      </c>
-      <c r="C41" s="313"/>
-      <c r="D41" s="263" t="s">
+        <v>74</v>
+      </c>
+      <c r="C41" s="322"/>
+      <c r="D41" s="270" t="s">
         <v>4</v>
       </c>
       <c r="E41" s="187"/>
       <c r="F41" s="187"/>
       <c r="G41" s="180"/>
-      <c r="H41" s="264" t="s">
-        <v>78</v>
+      <c r="H41" s="271" t="s">
+        <v>76</v>
       </c>
       <c r="I41" s="180"/>
       <c r="J41" s="111"/>
-      <c r="K41" s="129"/>
+      <c r="K41" s="132"/>
       <c r="L41" s="60"/>
       <c r="M41" s="60"/>
       <c r="N41" s="60"/>
@@ -6521,23 +6549,23 @@
       <c r="AB41" s="61"/>
     </row>
     <row r="42" spans="1:28" ht="52.5" customHeight="1" thickBot="1">
-      <c r="A42" s="325"/>
+      <c r="A42" s="334"/>
       <c r="B42" s="49" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C42" s="68"/>
-      <c r="D42" s="263" t="s">
+      <c r="D42" s="270" t="s">
         <v>4</v>
       </c>
       <c r="E42" s="187"/>
-      <c r="F42" s="269"/>
+      <c r="F42" s="276"/>
       <c r="G42" s="173"/>
       <c r="H42" s="184" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I42" s="185"/>
-      <c r="J42" s="127"/>
-      <c r="K42" s="128"/>
+      <c r="J42" s="130"/>
+      <c r="K42" s="131"/>
       <c r="L42" s="69"/>
       <c r="M42" s="69"/>
       <c r="N42" s="69"/>
@@ -6557,27 +6585,27 @@
       <c r="AB42" s="70"/>
     </row>
     <row r="43" spans="1:28" ht="64.5" customHeight="1">
-      <c r="A43" s="325"/>
+      <c r="A43" s="334"/>
       <c r="B43" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="314" t="s">
+      <c r="C43" s="323" t="s">
+        <v>77</v>
+      </c>
+      <c r="D43" s="190" t="s">
+        <v>78</v>
+      </c>
+      <c r="E43" s="272"/>
+      <c r="F43" s="273" t="s">
+        <v>290</v>
+      </c>
+      <c r="G43" s="238"/>
+      <c r="H43" s="274" t="s">
         <v>79</v>
       </c>
-      <c r="D43" s="190" t="s">
-        <v>80</v>
-      </c>
-      <c r="E43" s="265"/>
-      <c r="F43" s="266" t="s">
-        <v>314</v>
-      </c>
-      <c r="G43" s="192"/>
-      <c r="H43" s="267" t="s">
-        <v>81</v>
-      </c>
       <c r="I43" s="201"/>
-      <c r="J43" s="336"/>
-      <c r="K43" s="293"/>
+      <c r="J43" s="345"/>
+      <c r="K43" s="302"/>
       <c r="L43" s="60"/>
       <c r="M43" s="60"/>
       <c r="N43" s="60"/>
@@ -6597,21 +6625,21 @@
       <c r="AB43" s="61"/>
     </row>
     <row r="44" spans="1:28" ht="51.75" customHeight="1">
-      <c r="A44" s="325"/>
+      <c r="A44" s="334"/>
       <c r="B44" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="315"/>
+      <c r="C44" s="324"/>
       <c r="D44" s="179" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E44" s="187"/>
-      <c r="F44" s="337" t="s">
-        <v>248</v>
+      <c r="F44" s="346" t="s">
+        <v>245</v>
       </c>
       <c r="G44" s="217"/>
-      <c r="H44" s="271" t="s">
-        <v>245</v>
+      <c r="H44" s="279" t="s">
+        <v>242</v>
       </c>
       <c r="I44" s="173"/>
       <c r="J44" s="42"/>
@@ -6635,25 +6663,25 @@
       <c r="AB44" s="61"/>
     </row>
     <row r="45" spans="1:28" ht="49.5" customHeight="1" thickBot="1">
-      <c r="A45" s="325"/>
+      <c r="A45" s="334"/>
       <c r="B45" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C45" s="313"/>
-      <c r="D45" s="338" t="s">
-        <v>250</v>
+      <c r="C45" s="322"/>
+      <c r="D45" s="347" t="s">
+        <v>247</v>
       </c>
       <c r="E45" s="206"/>
-      <c r="F45" s="286" t="s">
-        <v>277</v>
-      </c>
-      <c r="G45" s="192"/>
-      <c r="H45" s="191" t="s">
-        <v>238</v>
-      </c>
-      <c r="I45" s="348"/>
-      <c r="J45" s="280"/>
-      <c r="K45" s="339"/>
+      <c r="F45" s="356" t="s">
+        <v>265</v>
+      </c>
+      <c r="G45" s="238"/>
+      <c r="H45" s="357" t="s">
+        <v>235</v>
+      </c>
+      <c r="I45" s="358"/>
+      <c r="J45" s="288"/>
+      <c r="K45" s="348"/>
       <c r="L45" s="60"/>
       <c r="M45" s="60"/>
       <c r="N45" s="60"/>
@@ -6673,27 +6701,27 @@
       <c r="AB45" s="61"/>
     </row>
     <row r="46" spans="1:28" ht="48.75" customHeight="1">
-      <c r="A46" s="325"/>
+      <c r="A46" s="334"/>
       <c r="B46" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C46" s="314" t="s">
+      <c r="C46" s="323" t="s">
         <v>16</v>
       </c>
       <c r="D46" s="186" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E46" s="187"/>
-      <c r="F46" s="340" t="s">
+      <c r="F46" s="349" t="s">
+        <v>256</v>
+      </c>
+      <c r="G46" s="238"/>
+      <c r="H46" s="347" t="s">
         <v>263</v>
-      </c>
-      <c r="G46" s="192"/>
-      <c r="H46" s="338" t="s">
-        <v>275</v>
       </c>
       <c r="I46" s="201"/>
       <c r="J46" s="179" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K46" s="208"/>
       <c r="L46" s="60"/>
@@ -6715,21 +6743,21 @@
       <c r="AB46" s="61"/>
     </row>
     <row r="47" spans="1:28" ht="48" customHeight="1">
-      <c r="A47" s="325"/>
+      <c r="A47" s="334"/>
       <c r="B47" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="C47" s="315"/>
+      <c r="C47" s="324"/>
       <c r="D47" s="207" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E47" s="187"/>
-      <c r="F47" s="239" t="s">
-        <v>228</v>
+      <c r="F47" s="244" t="s">
+        <v>225</v>
       </c>
       <c r="G47" s="201"/>
       <c r="H47" s="179" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I47" s="180"/>
       <c r="J47" s="81"/>
@@ -6753,21 +6781,21 @@
       <c r="AB47" s="61"/>
     </row>
     <row r="48" spans="1:28" ht="75" customHeight="1">
-      <c r="A48" s="325"/>
+      <c r="A48" s="334"/>
       <c r="B48" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="C48" s="315"/>
+      <c r="C48" s="324"/>
       <c r="D48" s="181" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E48" s="180"/>
-      <c r="F48" s="290" t="s">
-        <v>251</v>
+      <c r="F48" s="300" t="s">
+        <v>248</v>
       </c>
       <c r="G48" s="173"/>
       <c r="H48" s="172" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="I48" s="173"/>
       <c r="J48" s="172"/>
@@ -6791,26 +6819,26 @@
       <c r="AB48" s="61"/>
     </row>
     <row r="49" spans="1:28" ht="63" customHeight="1">
-      <c r="A49" s="325"/>
+      <c r="A49" s="334"/>
       <c r="B49" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="C49" s="315"/>
+      <c r="C49" s="324"/>
       <c r="D49" s="181" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E49" s="187"/>
       <c r="F49" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="G49" s="266" t="s">
-        <v>88</v>
-      </c>
-      <c r="H49" s="192"/>
-      <c r="I49" s="341" t="s">
-        <v>89</v>
-      </c>
-      <c r="J49" s="192"/>
+      <c r="G49" s="273" t="s">
+        <v>86</v>
+      </c>
+      <c r="H49" s="238"/>
+      <c r="I49" s="350" t="s">
+        <v>87</v>
+      </c>
+      <c r="J49" s="238"/>
       <c r="K49" s="120"/>
       <c r="L49" s="60"/>
       <c r="M49" s="60"/>
@@ -6831,11 +6859,11 @@
       <c r="AB49" s="61"/>
     </row>
     <row r="50" spans="1:28" ht="64.5" hidden="1" customHeight="1">
-      <c r="A50" s="325"/>
+      <c r="A50" s="334"/>
       <c r="B50" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="C50" s="315"/>
+        <v>88</v>
+      </c>
+      <c r="C50" s="324"/>
       <c r="D50" s="207"/>
       <c r="E50" s="187"/>
       <c r="F50" s="107"/>
@@ -6863,23 +6891,23 @@
       <c r="AB50" s="61"/>
     </row>
     <row r="51" spans="1:28" ht="48" customHeight="1">
-      <c r="A51" s="325"/>
+      <c r="A51" s="334"/>
       <c r="B51" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="C51" s="315"/>
-      <c r="D51" s="263" t="s">
-        <v>91</v>
+      <c r="C51" s="324"/>
+      <c r="D51" s="270" t="s">
+        <v>89</v>
       </c>
       <c r="E51" s="187"/>
       <c r="F51" s="191" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="G51" s="192"/>
-      <c r="H51" s="239" t="s">
-        <v>225</v>
-      </c>
-      <c r="I51" s="240"/>
+      <c r="H51" s="244" t="s">
+        <v>222</v>
+      </c>
+      <c r="I51" s="245"/>
       <c r="J51" s="57"/>
       <c r="K51" s="98"/>
       <c r="L51" s="60"/>
@@ -6901,13 +6929,13 @@
       <c r="AB51" s="61"/>
     </row>
     <row r="52" spans="1:28" ht="57.75" customHeight="1">
-      <c r="A52" s="325"/>
+      <c r="A52" s="334"/>
       <c r="B52" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C52" s="315"/>
+      <c r="C52" s="324"/>
       <c r="D52" s="207" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E52" s="187"/>
       <c r="F52" s="205" t="s">
@@ -6939,25 +6967,25 @@
       <c r="AB52" s="61"/>
     </row>
     <row r="53" spans="1:28" ht="49.5" customHeight="1">
-      <c r="A53" s="325"/>
+      <c r="A53" s="334"/>
       <c r="B53" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="C53" s="315"/>
+      <c r="C53" s="324"/>
       <c r="D53" s="181" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E53" s="180"/>
       <c r="F53" s="199" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G53" s="180"/>
-      <c r="H53" s="350" t="s">
-        <v>96</v>
+      <c r="H53" s="361" t="s">
+        <v>94</v>
       </c>
       <c r="I53" s="180"/>
       <c r="J53" s="172"/>
-      <c r="K53" s="339"/>
+      <c r="K53" s="348"/>
       <c r="L53" s="60"/>
       <c r="M53" s="60"/>
       <c r="N53" s="60"/>
@@ -6977,21 +7005,21 @@
       <c r="AB53" s="61"/>
     </row>
     <row r="54" spans="1:28" ht="53.25" customHeight="1" thickBot="1">
-      <c r="A54" s="325"/>
+      <c r="A54" s="334"/>
       <c r="B54" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="C54" s="313"/>
-      <c r="D54" s="342" t="s">
-        <v>102</v>
-      </c>
-      <c r="E54" s="343"/>
+      <c r="C54" s="322"/>
+      <c r="D54" s="351" t="s">
+        <v>100</v>
+      </c>
+      <c r="E54" s="278"/>
       <c r="F54" s="195" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G54" s="180"/>
       <c r="H54" s="209" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I54" s="180"/>
       <c r="J54" s="82"/>
@@ -7015,7 +7043,7 @@
       <c r="AB54" s="61"/>
     </row>
     <row r="55" spans="1:28" ht="48" customHeight="1">
-      <c r="A55" s="325"/>
+      <c r="A55" s="334"/>
       <c r="B55" s="42" t="s">
         <v>39</v>
       </c>
@@ -7023,15 +7051,15 @@
         <v>7</v>
       </c>
       <c r="D55" s="179" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E55" s="180"/>
       <c r="F55" s="179" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G55" s="180"/>
       <c r="H55" s="172" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I55" s="173"/>
       <c r="J55" s="109"/>
@@ -7055,26 +7083,26 @@
       <c r="AB55" s="61"/>
     </row>
     <row r="56" spans="1:28" ht="59.25" customHeight="1" thickBot="1">
-      <c r="A56" s="326"/>
+      <c r="A56" s="335"/>
       <c r="B56" s="102" t="s">
         <v>43</v>
       </c>
       <c r="C56" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="D56" s="291" t="s">
-        <v>103</v>
+      <c r="D56" s="301" t="s">
+        <v>101</v>
       </c>
       <c r="E56" s="213"/>
-      <c r="F56" s="284" t="s">
-        <v>104</v>
-      </c>
-      <c r="G56" s="360"/>
-      <c r="H56" s="361" t="s">
-        <v>308</v>
-      </c>
-      <c r="I56" s="361"/>
-      <c r="J56" s="165"/>
+      <c r="F56" s="293" t="s">
+        <v>102</v>
+      </c>
+      <c r="G56" s="370"/>
+      <c r="H56" s="371" t="s">
+        <v>284</v>
+      </c>
+      <c r="I56" s="371"/>
+      <c r="J56" s="126"/>
       <c r="K56" s="122"/>
       <c r="L56" s="60"/>
       <c r="M56" s="60"/>
@@ -7096,10 +7124,10 @@
     </row>
     <row r="57" spans="1:28" ht="21.75" customHeight="1" thickBot="1">
       <c r="A57" s="91"/>
-      <c r="B57" s="328" t="s">
-        <v>105</v>
-      </c>
-      <c r="C57" s="329"/>
+      <c r="B57" s="337" t="s">
+        <v>103</v>
+      </c>
+      <c r="C57" s="338"/>
       <c r="D57" s="92"/>
       <c r="E57" s="56"/>
       <c r="F57" s="56"/>
@@ -7127,36 +7155,36 @@
       <c r="AB57" s="61"/>
     </row>
     <row r="58" spans="1:28" ht="30.75" customHeight="1" thickBot="1">
-      <c r="A58" s="324" t="s">
-        <v>105</v>
+      <c r="A58" s="333" t="s">
+        <v>103</v>
       </c>
       <c r="B58" s="93" t="s">
         <v>47</v>
       </c>
       <c r="C58" s="115"/>
-      <c r="D58" s="153" t="s">
-        <v>299</v>
-      </c>
-      <c r="E58" s="154" t="s">
-        <v>300</v>
-      </c>
-      <c r="F58" s="154" t="s">
-        <v>301</v>
-      </c>
-      <c r="G58" s="154" t="s">
-        <v>302</v>
-      </c>
-      <c r="H58" s="155" t="s">
-        <v>303</v>
-      </c>
-      <c r="I58" s="155" t="s">
-        <v>304</v>
-      </c>
-      <c r="J58" s="155" t="s">
-        <v>305</v>
-      </c>
-      <c r="K58" s="156" t="s">
-        <v>306</v>
+      <c r="D58" s="154" t="s">
+        <v>275</v>
+      </c>
+      <c r="E58" s="155" t="s">
+        <v>276</v>
+      </c>
+      <c r="F58" s="155" t="s">
+        <v>277</v>
+      </c>
+      <c r="G58" s="155" t="s">
+        <v>278</v>
+      </c>
+      <c r="H58" s="156" t="s">
+        <v>279</v>
+      </c>
+      <c r="I58" s="156" t="s">
+        <v>280</v>
+      </c>
+      <c r="J58" s="156" t="s">
+        <v>281</v>
+      </c>
+      <c r="K58" s="157" t="s">
+        <v>282</v>
       </c>
       <c r="L58" s="60"/>
       <c r="M58" s="60"/>
@@ -7177,9 +7205,9 @@
       <c r="AB58" s="61"/>
     </row>
     <row r="59" spans="1:28" ht="44.25" customHeight="1">
-      <c r="A59" s="325"/>
+      <c r="A59" s="334"/>
       <c r="B59" s="44" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C59" s="45"/>
       <c r="D59" s="205" t="s">
@@ -7189,7 +7217,7 @@
       <c r="F59" s="206"/>
       <c r="G59" s="201"/>
       <c r="H59" s="202" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I59" s="201"/>
       <c r="J59" s="56"/>
@@ -7213,9 +7241,9 @@
       <c r="AB59" s="61"/>
     </row>
     <row r="60" spans="1:28" ht="53.25" customHeight="1">
-      <c r="A60" s="325"/>
+      <c r="A60" s="334"/>
       <c r="B60" s="44" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C60" s="45"/>
       <c r="D60" s="205" t="s">
@@ -7225,7 +7253,7 @@
       <c r="F60" s="206"/>
       <c r="G60" s="201"/>
       <c r="H60" s="179" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I60" s="187"/>
       <c r="J60" s="112"/>
@@ -7249,25 +7277,25 @@
       <c r="AB60" s="61"/>
     </row>
     <row r="61" spans="1:28" ht="56.25" customHeight="1">
-      <c r="A61" s="325"/>
+      <c r="A61" s="334"/>
       <c r="B61" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="C61" s="333" t="s">
+      <c r="C61" s="342" t="s">
         <v>7</v>
       </c>
       <c r="D61" s="202" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E61" s="201"/>
       <c r="F61" s="202" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G61" s="201"/>
-      <c r="H61" s="202" t="s">
-        <v>112</v>
-      </c>
-      <c r="I61" s="201"/>
+      <c r="H61" s="285" t="s">
+        <v>110</v>
+      </c>
+      <c r="I61" s="217"/>
       <c r="J61" s="83"/>
       <c r="K61" s="98"/>
       <c r="L61" s="60"/>
@@ -7289,24 +7317,24 @@
       <c r="AB61" s="61"/>
     </row>
     <row r="62" spans="1:28" ht="60" customHeight="1">
-      <c r="A62" s="325"/>
+      <c r="A62" s="334"/>
       <c r="B62" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="C62" s="334"/>
-      <c r="D62" s="199" t="s">
-        <v>282</v>
-      </c>
-      <c r="E62" s="180"/>
+      <c r="C62" s="343"/>
+      <c r="D62" s="375" t="s">
+        <v>303</v>
+      </c>
+      <c r="E62" s="278"/>
       <c r="F62" s="193" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G62" s="194"/>
-      <c r="H62" s="96"/>
-      <c r="I62" s="179" t="s">
-        <v>114</v>
-      </c>
-      <c r="J62" s="180"/>
+      <c r="H62" s="243" t="s">
+        <v>112</v>
+      </c>
+      <c r="I62" s="243"/>
+      <c r="J62" s="171"/>
       <c r="K62" s="99"/>
       <c r="L62" s="60"/>
       <c r="M62" s="60"/>
@@ -7327,24 +7355,24 @@
       <c r="AB62" s="61"/>
     </row>
     <row r="63" spans="1:28" ht="67.5" customHeight="1">
-      <c r="A63" s="325"/>
+      <c r="A63" s="334"/>
       <c r="B63" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="C63" s="335"/>
+      <c r="C63" s="344"/>
       <c r="D63" s="199" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E63" s="180"/>
       <c r="F63" s="179" t="s">
-        <v>237</v>
-      </c>
-      <c r="G63" s="211"/>
-      <c r="H63" s="76"/>
-      <c r="I63" s="179" t="s">
-        <v>116</v>
-      </c>
-      <c r="J63" s="180"/>
+        <v>234</v>
+      </c>
+      <c r="G63" s="374"/>
+      <c r="H63" s="243" t="s">
+        <v>114</v>
+      </c>
+      <c r="I63" s="243"/>
+      <c r="J63" s="171"/>
       <c r="K63" s="100"/>
       <c r="L63" s="60"/>
       <c r="M63" s="60"/>
@@ -7365,27 +7393,27 @@
       <c r="AB63" s="61"/>
     </row>
     <row r="64" spans="1:28" ht="54" customHeight="1">
-      <c r="A64" s="325"/>
+      <c r="A64" s="334"/>
       <c r="B64" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="C64" s="330" t="s">
+      <c r="C64" s="339" t="s">
         <v>16</v>
       </c>
       <c r="D64" s="209" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E64" s="180"/>
       <c r="F64" s="179" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G64" s="180"/>
-      <c r="H64" s="179" t="s">
-        <v>117</v>
-      </c>
-      <c r="I64" s="180"/>
+      <c r="H64" s="202" t="s">
+        <v>115</v>
+      </c>
+      <c r="I64" s="201"/>
       <c r="J64" s="179" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K64" s="208"/>
       <c r="L64" s="60"/>
@@ -7407,27 +7435,27 @@
       <c r="AB64" s="61"/>
     </row>
     <row r="65" spans="1:28" ht="48" customHeight="1">
-      <c r="A65" s="325"/>
+      <c r="A65" s="334"/>
       <c r="B65" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="C65" s="334"/>
-      <c r="D65" s="354" t="s">
-        <v>234</v>
+      <c r="C65" s="343"/>
+      <c r="D65" s="365" t="s">
+        <v>231</v>
       </c>
       <c r="E65" s="180"/>
       <c r="F65" s="199" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G65" s="180"/>
       <c r="H65" s="179" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I65" s="180"/>
-      <c r="J65" s="352" t="s">
-        <v>122</v>
-      </c>
-      <c r="K65" s="353"/>
+      <c r="J65" s="363" t="s">
+        <v>120</v>
+      </c>
+      <c r="K65" s="364"/>
       <c r="L65" s="60"/>
       <c r="M65" s="60"/>
       <c r="N65" s="60"/>
@@ -7447,25 +7475,25 @@
       <c r="AB65" s="61"/>
     </row>
     <row r="66" spans="1:28" ht="54" customHeight="1">
-      <c r="A66" s="325"/>
+      <c r="A66" s="334"/>
       <c r="B66" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C66" s="334"/>
+      <c r="C66" s="343"/>
       <c r="D66" s="174" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="E66" s="178"/>
       <c r="F66" s="190" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G66" s="187"/>
       <c r="H66" s="179" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I66" s="180"/>
       <c r="J66" s="179" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="K66" s="208"/>
       <c r="L66" s="60"/>
@@ -7487,27 +7515,27 @@
       <c r="AB66" s="61"/>
     </row>
     <row r="67" spans="1:28" ht="78.75" customHeight="1">
-      <c r="A67" s="325"/>
+      <c r="A67" s="334"/>
       <c r="B67" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C67" s="334"/>
-      <c r="D67" s="351" t="s">
-        <v>236</v>
+      <c r="C67" s="343"/>
+      <c r="D67" s="362" t="s">
+        <v>233</v>
       </c>
       <c r="E67" s="206"/>
       <c r="F67" s="50" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="G67" s="110" t="s">
-        <v>316</v>
-      </c>
-      <c r="H67" s="362" t="s">
-        <v>235</v>
-      </c>
-      <c r="I67" s="363"/>
+        <v>292</v>
+      </c>
+      <c r="H67" s="372" t="s">
+        <v>232</v>
+      </c>
+      <c r="I67" s="373"/>
       <c r="J67" s="202" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K67" s="203"/>
       <c r="L67" s="60"/>
@@ -7529,25 +7557,25 @@
       <c r="AB67" s="61"/>
     </row>
     <row r="68" spans="1:28" ht="57" customHeight="1">
-      <c r="A68" s="325"/>
+      <c r="A68" s="334"/>
       <c r="B68" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="C68" s="334"/>
+      <c r="C68" s="343"/>
       <c r="D68" s="202" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E68" s="201"/>
-      <c r="F68" s="281" t="s">
-        <v>276</v>
+      <c r="F68" s="289" t="s">
+        <v>264</v>
       </c>
       <c r="G68" s="201"/>
       <c r="H68" s="199" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="I68" s="180"/>
       <c r="J68" s="179" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K68" s="208"/>
       <c r="L68" s="60"/>
@@ -7569,13 +7597,13 @@
       <c r="AB68" s="61"/>
     </row>
     <row r="69" spans="1:28" ht="49.5" customHeight="1">
-      <c r="A69" s="325"/>
+      <c r="A69" s="334"/>
       <c r="B69" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="C69" s="335"/>
+      <c r="C69" s="344"/>
       <c r="D69" s="179" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E69" s="180"/>
       <c r="F69" s="179" t="s">
@@ -7607,23 +7635,23 @@
       <c r="AB69" s="61"/>
     </row>
     <row r="70" spans="1:28" ht="53.25" customHeight="1">
-      <c r="A70" s="325"/>
+      <c r="A70" s="334"/>
       <c r="B70" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="C70" s="330" t="s">
+      <c r="C70" s="339" t="s">
         <v>16</v>
       </c>
       <c r="D70" s="179" t="s">
-        <v>242</v>
-      </c>
-      <c r="E70" s="282"/>
-      <c r="F70" s="179" t="s">
-        <v>274</v>
-      </c>
-      <c r="G70" s="180"/>
-      <c r="H70" s="283" t="s">
-        <v>128</v>
+        <v>239</v>
+      </c>
+      <c r="E70" s="290"/>
+      <c r="F70" s="291" t="s">
+        <v>306</v>
+      </c>
+      <c r="G70" s="278"/>
+      <c r="H70" s="292" t="s">
+        <v>126</v>
       </c>
       <c r="I70" s="180"/>
       <c r="J70" s="179"/>
@@ -7647,21 +7675,21 @@
       <c r="AB70" s="61"/>
     </row>
     <row r="71" spans="1:28" ht="51" customHeight="1">
-      <c r="A71" s="325"/>
+      <c r="A71" s="334"/>
       <c r="B71" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="C71" s="335"/>
+      <c r="C71" s="344"/>
       <c r="D71" s="190" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E71" s="187"/>
       <c r="F71" s="199" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G71" s="180"/>
       <c r="H71" s="202" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I71" s="201"/>
       <c r="J71" s="179"/>
@@ -7685,23 +7713,23 @@
       <c r="AB71" s="61"/>
     </row>
     <row r="72" spans="1:28" ht="50.25" customHeight="1">
-      <c r="A72" s="325"/>
+      <c r="A72" s="334"/>
       <c r="B72" s="42" t="s">
         <v>39</v>
       </c>
       <c r="C72" s="46" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D72" s="179" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E72" s="180"/>
       <c r="F72" s="179" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G72" s="180"/>
       <c r="H72" s="179" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I72" s="180"/>
       <c r="J72" s="55"/>
@@ -7724,26 +7752,26 @@
       <c r="AA72" s="61"/>
       <c r="AB72" s="61"/>
     </row>
-    <row r="73" spans="1:28" ht="54" thickBot="1">
-      <c r="A73" s="326"/>
+    <row r="73" spans="1:28" ht="53.25" thickBot="1">
+      <c r="A73" s="335"/>
       <c r="B73" s="102" t="s">
         <v>43</v>
       </c>
       <c r="C73" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="D73" s="355" t="s">
-        <v>246</v>
+      <c r="D73" s="366" t="s">
+        <v>243</v>
       </c>
       <c r="E73" s="213"/>
-      <c r="F73" s="291" t="s">
-        <v>317</v>
+      <c r="F73" s="301" t="s">
+        <v>293</v>
       </c>
       <c r="G73" s="213"/>
-      <c r="H73" s="284" t="s">
-        <v>127</v>
-      </c>
-      <c r="I73" s="285"/>
+      <c r="H73" s="293" t="s">
+        <v>125</v>
+      </c>
+      <c r="I73" s="294"/>
       <c r="J73" s="104"/>
       <c r="K73" s="105"/>
       <c r="L73" s="60"/>
@@ -7766,10 +7794,10 @@
     </row>
     <row r="74" spans="1:28" ht="15.75" customHeight="1" thickBot="1">
       <c r="A74" s="91"/>
-      <c r="B74" s="328" t="s">
-        <v>135</v>
-      </c>
-      <c r="C74" s="329"/>
+      <c r="B74" s="337" t="s">
+        <v>133</v>
+      </c>
+      <c r="C74" s="338"/>
       <c r="D74" s="92"/>
       <c r="E74" s="56"/>
       <c r="F74" s="56"/>
@@ -7797,36 +7825,36 @@
       <c r="AB74" s="61"/>
     </row>
     <row r="75" spans="1:28" ht="27" customHeight="1" thickBot="1">
-      <c r="A75" s="324" t="s">
-        <v>136</v>
-      </c>
-      <c r="B75" s="157" t="s">
+      <c r="A75" s="333" t="s">
+        <v>134</v>
+      </c>
+      <c r="B75" s="158" t="s">
         <v>47</v>
       </c>
-      <c r="C75" s="158"/>
-      <c r="D75" s="153" t="s">
-        <v>299</v>
-      </c>
-      <c r="E75" s="154" t="s">
-        <v>300</v>
-      </c>
-      <c r="F75" s="154" t="s">
-        <v>301</v>
-      </c>
-      <c r="G75" s="154" t="s">
-        <v>302</v>
-      </c>
-      <c r="H75" s="155" t="s">
-        <v>303</v>
-      </c>
-      <c r="I75" s="155" t="s">
-        <v>304</v>
-      </c>
-      <c r="J75" s="155" t="s">
-        <v>305</v>
-      </c>
-      <c r="K75" s="156" t="s">
-        <v>306</v>
+      <c r="C75" s="159"/>
+      <c r="D75" s="154" t="s">
+        <v>275</v>
+      </c>
+      <c r="E75" s="155" t="s">
+        <v>276</v>
+      </c>
+      <c r="F75" s="155" t="s">
+        <v>277</v>
+      </c>
+      <c r="G75" s="155" t="s">
+        <v>278</v>
+      </c>
+      <c r="H75" s="156" t="s">
+        <v>279</v>
+      </c>
+      <c r="I75" s="156" t="s">
+        <v>280</v>
+      </c>
+      <c r="J75" s="156" t="s">
+        <v>281</v>
+      </c>
+      <c r="K75" s="157" t="s">
+        <v>282</v>
       </c>
       <c r="L75" s="60"/>
       <c r="M75" s="60"/>
@@ -7846,24 +7874,24 @@
       <c r="AA75" s="61"/>
       <c r="AB75" s="61"/>
     </row>
-    <row r="76" spans="1:28" ht="74.25" thickBot="1">
-      <c r="A76" s="325"/>
+    <row r="76" spans="1:28" ht="73.5" thickBot="1">
+      <c r="A76" s="334"/>
       <c r="B76" s="47" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C76" s="48" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="179"/>
       <c r="E76" s="180"/>
-      <c r="F76" s="344" t="s">
-        <v>285</v>
-      </c>
-      <c r="G76" s="345"/>
-      <c r="H76" s="169"/>
-      <c r="I76" s="280"/>
+      <c r="F76" s="352" t="s">
+        <v>271</v>
+      </c>
+      <c r="G76" s="353"/>
+      <c r="H76" s="168"/>
+      <c r="I76" s="288"/>
       <c r="J76" s="180"/>
-      <c r="K76" s="159"/>
+      <c r="K76" s="160"/>
       <c r="L76" s="60"/>
       <c r="M76" s="60"/>
       <c r="N76" s="60"/>
@@ -7883,25 +7911,25 @@
       <c r="AB76" s="61"/>
     </row>
     <row r="77" spans="1:28" ht="54.75" customHeight="1" thickBot="1">
-      <c r="A77" s="325"/>
+      <c r="A77" s="334"/>
       <c r="B77" s="49" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C77" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="D77" s="289" t="s">
+      <c r="D77" s="299" t="s">
         <v>4</v>
       </c>
-      <c r="E77" s="269"/>
-      <c r="F77" s="269"/>
-      <c r="G77" s="269"/>
-      <c r="H77" s="359" t="s">
-        <v>253</v>
-      </c>
-      <c r="I77" s="359"/>
-      <c r="J77" s="123"/>
-      <c r="K77" s="160"/>
+      <c r="E77" s="276"/>
+      <c r="F77" s="276"/>
+      <c r="G77" s="276"/>
+      <c r="H77" s="369" t="s">
+        <v>250</v>
+      </c>
+      <c r="I77" s="369"/>
+      <c r="J77" s="96"/>
+      <c r="K77" s="161"/>
       <c r="L77" s="60"/>
       <c r="M77" s="60"/>
       <c r="N77" s="60"/>
@@ -7921,26 +7949,26 @@
       <c r="AB77" s="61"/>
     </row>
     <row r="78" spans="1:28" ht="50.25" customHeight="1">
-      <c r="A78" s="325"/>
+      <c r="A78" s="334"/>
       <c r="B78" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="C78" s="314" t="s">
-        <v>139</v>
+      <c r="C78" s="323" t="s">
+        <v>137</v>
       </c>
       <c r="D78" s="181" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E78" s="180"/>
       <c r="F78" s="179" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G78" s="187"/>
-      <c r="H78" s="359" t="s">
-        <v>222</v>
-      </c>
-      <c r="I78" s="359"/>
-      <c r="J78" s="145"/>
+      <c r="H78" s="369" t="s">
+        <v>219</v>
+      </c>
+      <c r="I78" s="369"/>
+      <c r="J78" s="149"/>
       <c r="K78" s="117"/>
       <c r="L78" s="60"/>
       <c r="M78" s="60"/>
@@ -7961,24 +7989,24 @@
       <c r="AB78" s="61"/>
     </row>
     <row r="79" spans="1:28" ht="50.25" customHeight="1">
-      <c r="A79" s="325"/>
+      <c r="A79" s="334"/>
       <c r="B79" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="C79" s="315"/>
-      <c r="D79" s="267" t="s">
-        <v>142</v>
+      <c r="C79" s="324"/>
+      <c r="D79" s="274" t="s">
+        <v>140</v>
       </c>
       <c r="E79" s="201"/>
-      <c r="F79" s="290" t="s">
-        <v>56</v>
-      </c>
-      <c r="G79" s="269"/>
-      <c r="H79" s="266" t="s">
-        <v>143</v>
-      </c>
-      <c r="I79" s="266"/>
-      <c r="J79" s="147"/>
+      <c r="F79" s="300" t="s">
+        <v>54</v>
+      </c>
+      <c r="G79" s="276"/>
+      <c r="H79" s="273" t="s">
+        <v>141</v>
+      </c>
+      <c r="I79" s="273"/>
+      <c r="J79" s="150"/>
       <c r="K79" s="120"/>
       <c r="L79" s="60"/>
       <c r="M79" s="60"/>
@@ -7999,24 +8027,24 @@
       <c r="AB79" s="61"/>
     </row>
     <row r="80" spans="1:28" ht="52.5" customHeight="1" thickBot="1">
-      <c r="A80" s="325"/>
+      <c r="A80" s="334"/>
       <c r="B80" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C80" s="313"/>
-      <c r="D80" s="267" t="s">
-        <v>144</v>
+      <c r="C80" s="322"/>
+      <c r="D80" s="274" t="s">
+        <v>142</v>
       </c>
       <c r="E80" s="201"/>
-      <c r="F80" s="209" t="s">
-        <v>145</v>
-      </c>
-      <c r="G80" s="187"/>
-      <c r="H80" s="266" t="s">
-        <v>146</v>
-      </c>
-      <c r="I80" s="266"/>
-      <c r="J80" s="147"/>
+      <c r="F80" s="277" t="s">
+        <v>311</v>
+      </c>
+      <c r="G80" s="236"/>
+      <c r="H80" s="273" t="s">
+        <v>143</v>
+      </c>
+      <c r="I80" s="273"/>
+      <c r="J80" s="150"/>
       <c r="K80" s="120"/>
       <c r="L80" s="60"/>
       <c r="M80" s="60"/>
@@ -8037,26 +8065,26 @@
       <c r="AB80" s="61"/>
     </row>
     <row r="81" spans="1:28" ht="52.5" customHeight="1">
-      <c r="A81" s="325"/>
+      <c r="A81" s="334"/>
       <c r="B81" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C81" s="314" t="s">
+      <c r="C81" s="323" t="s">
         <v>16</v>
       </c>
       <c r="D81" s="207" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E81" s="180"/>
       <c r="F81" s="172" t="s">
-        <v>220</v>
-      </c>
-      <c r="G81" s="269"/>
-      <c r="H81" s="266" t="s">
-        <v>221</v>
-      </c>
-      <c r="I81" s="266"/>
-      <c r="J81" s="146"/>
+        <v>217</v>
+      </c>
+      <c r="G81" s="276"/>
+      <c r="H81" s="273" t="s">
+        <v>218</v>
+      </c>
+      <c r="I81" s="273"/>
+      <c r="J81" s="124"/>
       <c r="K81" s="100"/>
       <c r="L81" s="60"/>
       <c r="M81" s="60"/>
@@ -8077,24 +8105,24 @@
       <c r="AB81" s="61"/>
     </row>
     <row r="82" spans="1:28" ht="61.5" customHeight="1">
-      <c r="A82" s="325"/>
+      <c r="A82" s="334"/>
       <c r="B82" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="C82" s="315"/>
-      <c r="D82" s="263" t="s">
-        <v>318</v>
+      <c r="C82" s="324"/>
+      <c r="D82" s="270" t="s">
+        <v>294</v>
       </c>
       <c r="E82" s="187"/>
-      <c r="F82" s="286" t="s">
-        <v>249</v>
-      </c>
-      <c r="G82" s="287"/>
-      <c r="H82" s="266" t="s">
-        <v>148</v>
-      </c>
-      <c r="I82" s="266"/>
-      <c r="J82" s="148"/>
+      <c r="F82" s="295" t="s">
+        <v>309</v>
+      </c>
+      <c r="G82" s="296"/>
+      <c r="H82" s="273" t="s">
+        <v>145</v>
+      </c>
+      <c r="I82" s="273"/>
+      <c r="J82" s="123"/>
       <c r="K82" s="100"/>
       <c r="L82" s="60"/>
       <c r="M82" s="60"/>
@@ -8115,25 +8143,25 @@
       <c r="AB82" s="61"/>
     </row>
     <row r="83" spans="1:28" ht="52.5" customHeight="1">
-      <c r="A83" s="325"/>
+      <c r="A83" s="334"/>
       <c r="B83" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="C83" s="315"/>
-      <c r="D83" s="288" t="s">
-        <v>283</v>
-      </c>
-      <c r="E83" s="269"/>
+      <c r="C83" s="324"/>
+      <c r="D83" s="297" t="s">
+        <v>307</v>
+      </c>
+      <c r="E83" s="298"/>
       <c r="F83" s="179" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="G83" s="187"/>
-      <c r="H83" s="266" t="s">
-        <v>150</v>
-      </c>
-      <c r="I83" s="266"/>
-      <c r="J83" s="148"/>
-      <c r="K83" s="141"/>
+      <c r="H83" s="273" t="s">
+        <v>147</v>
+      </c>
+      <c r="I83" s="273"/>
+      <c r="J83" s="123"/>
+      <c r="K83" s="144"/>
       <c r="L83" s="60"/>
       <c r="M83" s="60"/>
       <c r="N83" s="60"/>
@@ -8153,24 +8181,24 @@
       <c r="AB83" s="61"/>
     </row>
     <row r="84" spans="1:28" ht="51.75" customHeight="1">
-      <c r="A84" s="325"/>
+      <c r="A84" s="334"/>
       <c r="B84" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="C84" s="315"/>
+      <c r="C84" s="324"/>
       <c r="D84" s="190" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E84" s="187"/>
-      <c r="F84" s="286" t="s">
-        <v>151</v>
-      </c>
-      <c r="G84" s="287"/>
-      <c r="H84" s="266" t="s">
-        <v>152</v>
-      </c>
-      <c r="I84" s="266"/>
-      <c r="J84" s="148"/>
+      <c r="F84" s="356" t="s">
+        <v>148</v>
+      </c>
+      <c r="G84" s="359"/>
+      <c r="H84" s="273" t="s">
+        <v>149</v>
+      </c>
+      <c r="I84" s="273"/>
+      <c r="J84" s="123"/>
       <c r="K84" s="100"/>
       <c r="L84" s="60"/>
       <c r="M84" s="60"/>
@@ -8191,24 +8219,24 @@
       <c r="AB84" s="61"/>
     </row>
     <row r="85" spans="1:28" ht="63" customHeight="1">
-      <c r="A85" s="325"/>
+      <c r="A85" s="334"/>
       <c r="B85" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="C85" s="315"/>
+      <c r="C85" s="324"/>
       <c r="D85" s="179" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E85" s="187"/>
       <c r="F85" s="202" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G85" s="206"/>
-      <c r="H85" s="266" t="s">
-        <v>307</v>
-      </c>
-      <c r="I85" s="266"/>
-      <c r="J85" s="148"/>
+      <c r="H85" s="273" t="s">
+        <v>283</v>
+      </c>
+      <c r="I85" s="273"/>
+      <c r="J85" s="123"/>
       <c r="K85" s="100"/>
       <c r="L85" s="60"/>
       <c r="M85" s="60"/>
@@ -8228,26 +8256,26 @@
       <c r="AA85" s="61"/>
       <c r="AB85" s="61"/>
     </row>
-    <row r="86" spans="1:28" ht="49.5" customHeight="1">
-      <c r="A86" s="325"/>
+    <row r="86" spans="1:28" ht="60.75" customHeight="1">
+      <c r="A86" s="334"/>
       <c r="B86" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C86" s="315"/>
+      <c r="C86" s="324"/>
       <c r="D86" s="207" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E86" s="180"/>
       <c r="F86" s="205" t="s">
         <v>4</v>
       </c>
       <c r="G86" s="206"/>
-      <c r="H86" s="358" t="s">
-        <v>155</v>
-      </c>
-      <c r="I86" s="358"/>
-      <c r="J86" s="146"/>
-      <c r="K86" s="161"/>
+      <c r="H86" s="368" t="s">
+        <v>152</v>
+      </c>
+      <c r="I86" s="368"/>
+      <c r="J86" s="124"/>
+      <c r="K86" s="162"/>
       <c r="L86" s="60"/>
       <c r="M86" s="60"/>
       <c r="N86" s="60"/>
@@ -8267,24 +8295,24 @@
       <c r="AB86" s="61"/>
     </row>
     <row r="87" spans="1:28" ht="45.75" customHeight="1">
-      <c r="A87" s="325"/>
+      <c r="A87" s="334"/>
       <c r="B87" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="C87" s="315"/>
+      <c r="C87" s="324"/>
       <c r="D87" s="207" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E87" s="180"/>
       <c r="F87" s="199" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G87" s="187"/>
-      <c r="H87" s="266" t="s">
-        <v>158</v>
-      </c>
-      <c r="I87" s="266"/>
-      <c r="J87" s="148"/>
+      <c r="H87" s="273" t="s">
+        <v>155</v>
+      </c>
+      <c r="I87" s="273"/>
+      <c r="J87" s="123"/>
       <c r="K87" s="100"/>
       <c r="L87" s="60"/>
       <c r="M87" s="60"/>
@@ -8305,18 +8333,18 @@
       <c r="AB87" s="61"/>
     </row>
     <row r="88" spans="1:28" ht="64.5" hidden="1" customHeight="1">
-      <c r="A88" s="325"/>
+      <c r="A88" s="334"/>
       <c r="B88" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="C88" s="315"/>
+      <c r="C88" s="324"/>
       <c r="D88" s="84"/>
       <c r="E88" s="51"/>
       <c r="F88" s="51"/>
       <c r="G88" s="85"/>
-      <c r="H88" s="151"/>
-      <c r="I88" s="152"/>
-      <c r="J88" s="149"/>
+      <c r="H88" s="152"/>
+      <c r="I88" s="153"/>
+      <c r="J88" s="151"/>
       <c r="K88" s="100"/>
       <c r="L88" s="60"/>
       <c r="M88" s="60"/>
@@ -8337,24 +8365,24 @@
       <c r="AB88" s="61"/>
     </row>
     <row r="89" spans="1:28" ht="58.5" customHeight="1" thickBot="1">
-      <c r="A89" s="325"/>
+      <c r="A89" s="334"/>
       <c r="B89" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="C89" s="313"/>
+      <c r="C89" s="322"/>
       <c r="D89" s="207" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E89" s="180"/>
       <c r="F89" s="179" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G89" s="187"/>
-      <c r="H89" s="266" t="s">
-        <v>161</v>
-      </c>
-      <c r="I89" s="266"/>
-      <c r="J89" s="150"/>
+      <c r="H89" s="273" t="s">
+        <v>158</v>
+      </c>
+      <c r="I89" s="273"/>
+      <c r="J89" s="125"/>
       <c r="K89" s="100"/>
       <c r="L89" s="60"/>
       <c r="M89" s="60"/>
@@ -8375,26 +8403,26 @@
       <c r="AB89" s="61"/>
     </row>
     <row r="90" spans="1:28" ht="50.25" customHeight="1" thickBot="1">
-      <c r="A90" s="325"/>
+      <c r="A90" s="334"/>
       <c r="B90" s="35" t="s">
         <v>39</v>
       </c>
       <c r="C90" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="D90" s="349" t="s">
-        <v>162</v>
-      </c>
-      <c r="E90" s="329"/>
+      <c r="D90" s="360" t="s">
+        <v>159</v>
+      </c>
+      <c r="E90" s="338"/>
       <c r="F90" s="179" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G90" s="187"/>
-      <c r="H90" s="266" t="s">
-        <v>164</v>
-      </c>
-      <c r="I90" s="266"/>
-      <c r="J90" s="148"/>
+      <c r="H90" s="273" t="s">
+        <v>161</v>
+      </c>
+      <c r="I90" s="273"/>
+      <c r="J90" s="123"/>
       <c r="K90" s="100"/>
       <c r="L90" s="60"/>
       <c r="M90" s="60"/>
@@ -8415,25 +8443,25 @@
       <c r="AB90" s="61"/>
     </row>
     <row r="91" spans="1:28" ht="46.5" customHeight="1" thickBot="1">
-      <c r="A91" s="326"/>
-      <c r="B91" s="162" t="s">
+      <c r="A91" s="335"/>
+      <c r="B91" s="148" t="s">
         <v>43</v>
       </c>
       <c r="C91" s="163" t="s">
         <v>16</v>
       </c>
-      <c r="D91" s="346" t="s">
-        <v>165</v>
+      <c r="D91" s="354" t="s">
+        <v>162</v>
       </c>
       <c r="E91" s="213"/>
-      <c r="F91" s="291" t="s">
-        <v>166</v>
-      </c>
-      <c r="G91" s="347"/>
-      <c r="H91" s="357" t="s">
-        <v>167</v>
-      </c>
-      <c r="I91" s="357"/>
+      <c r="F91" s="301" t="s">
+        <v>163</v>
+      </c>
+      <c r="G91" s="355"/>
+      <c r="H91" s="367" t="s">
+        <v>164</v>
+      </c>
+      <c r="I91" s="367"/>
       <c r="J91" s="164"/>
       <c r="K91" s="105"/>
       <c r="L91" s="60"/>
@@ -8670,8 +8698,8 @@
       <c r="C99" s="86"/>
       <c r="D99" s="88"/>
       <c r="E99" s="88"/>
-      <c r="F99" s="88"/>
-      <c r="G99" s="88"/>
+      <c r="F99" s="231"/>
+      <c r="G99" s="232"/>
       <c r="H99" s="88"/>
       <c r="I99" s="88"/>
       <c r="J99" s="88"/>
@@ -35725,7 +35753,7 @@
       <c r="AB1000" s="90"/>
     </row>
   </sheetData>
-  <mergeCells count="271">
+  <mergeCells count="272">
     <mergeCell ref="D73:E73"/>
     <mergeCell ref="H66:I66"/>
     <mergeCell ref="J66:K66"/>
@@ -35750,10 +35778,8 @@
     <mergeCell ref="F63:G63"/>
     <mergeCell ref="H64:I64"/>
     <mergeCell ref="D62:E62"/>
-    <mergeCell ref="I62:J62"/>
     <mergeCell ref="D63:E63"/>
     <mergeCell ref="F65:G65"/>
-    <mergeCell ref="I63:J63"/>
     <mergeCell ref="D64:E64"/>
     <mergeCell ref="D67:E67"/>
     <mergeCell ref="J65:K65"/>
@@ -35899,8 +35925,6 @@
     <mergeCell ref="D80:E80"/>
     <mergeCell ref="D76:E76"/>
     <mergeCell ref="D77:G77"/>
-    <mergeCell ref="D41:G41"/>
-    <mergeCell ref="H41:I41"/>
     <mergeCell ref="D43:E43"/>
     <mergeCell ref="F43:G43"/>
     <mergeCell ref="H43:I43"/>
@@ -35923,10 +35947,16 @@
     <mergeCell ref="J27:K27"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="D41:G41"/>
+    <mergeCell ref="H41:I41"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="D33:E33"/>
@@ -35936,17 +35966,7 @@
     <mergeCell ref="F35:G35"/>
     <mergeCell ref="H35:I35"/>
     <mergeCell ref="J35:K35"/>
-    <mergeCell ref="D40:G40"/>
-    <mergeCell ref="H40:I40"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="H30:I30"/>
     <mergeCell ref="H29:I29"/>
     <mergeCell ref="J29:K29"/>
     <mergeCell ref="D29:E29"/>
@@ -35954,7 +35974,7 @@
     <mergeCell ref="H23:I23"/>
     <mergeCell ref="D24:G24"/>
     <mergeCell ref="H24:I24"/>
-    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F99:G99"/>
     <mergeCell ref="H25:I25"/>
     <mergeCell ref="J25:K25"/>
     <mergeCell ref="D25:E25"/>
@@ -35962,6 +35982,15 @@
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="H26:I26"/>
     <mergeCell ref="J26:K26"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="H40:I40"/>
     <mergeCell ref="H17:I17"/>
     <mergeCell ref="J17:K17"/>
     <mergeCell ref="H18:I18"/>
@@ -36017,389 +36046,392 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A1" s="364" t="s">
-        <v>168</v>
-      </c>
-      <c r="B1" s="365"/>
-      <c r="C1" s="365"/>
-      <c r="D1" s="365"/>
-      <c r="E1" s="365"/>
-      <c r="F1" s="366"/>
+      <c r="A1" s="376" t="s">
+        <v>165</v>
+      </c>
+      <c r="B1" s="377"/>
+      <c r="C1" s="377"/>
+      <c r="D1" s="377"/>
+      <c r="E1" s="377"/>
+      <c r="F1" s="378"/>
     </row>
     <row r="2" spans="1:9" ht="18">
-      <c r="A2" s="367" t="s">
-        <v>168</v>
+      <c r="A2" s="379" t="s">
+        <v>165</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="170" t="s">
+      <c r="D2" s="169" t="s">
+        <v>295</v>
+      </c>
+      <c r="E2" s="169" t="s">
+        <v>296</v>
+      </c>
+      <c r="F2" s="170" t="s">
+        <v>297</v>
+      </c>
+      <c r="G2" s="170" t="s">
+        <v>322</v>
+      </c>
+      <c r="H2" s="170" t="s">
+        <v>279</v>
+      </c>
+      <c r="I2" s="170" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="90">
+      <c r="A3" s="380"/>
+      <c r="B3" s="129" t="s">
+        <v>273</v>
+      </c>
+      <c r="C3" s="127"/>
+      <c r="D3" s="128" t="s">
+        <v>321</v>
+      </c>
+      <c r="E3" s="128" t="s">
+        <v>320</v>
+      </c>
+      <c r="F3" s="128" t="s">
         <v>319</v>
       </c>
-      <c r="E2" s="170" t="s">
-        <v>320</v>
-      </c>
-      <c r="F2" s="171" t="s">
-        <v>321</v>
-      </c>
-      <c r="G2" s="171" t="s">
-        <v>322</v>
-      </c>
-      <c r="H2" s="171" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="72">
-      <c r="A3" s="368"/>
-      <c r="B3" s="126" t="s">
-        <v>297</v>
-      </c>
-      <c r="C3" s="124"/>
-      <c r="D3" s="125" t="s">
-        <v>286</v>
-      </c>
-      <c r="E3" s="125" t="s">
-        <v>289</v>
-      </c>
-      <c r="F3" s="125" t="s">
-        <v>290</v>
-      </c>
-      <c r="G3" s="125" t="s">
-        <v>291</v>
-      </c>
-      <c r="H3" s="125" t="s">
-        <v>292</v>
-      </c>
-      <c r="I3" s="125" t="s">
-        <v>287</v>
+      <c r="G3" s="128" t="s">
+        <v>318</v>
+      </c>
+      <c r="H3" s="128" t="s">
+        <v>317</v>
+      </c>
+      <c r="I3" s="128" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="72">
-      <c r="A4" s="368"/>
-      <c r="B4" s="126" t="s">
-        <v>297</v>
-      </c>
-      <c r="C4" s="124"/>
-      <c r="D4" s="125" t="s">
-        <v>288</v>
-      </c>
-      <c r="E4" s="125" t="s">
-        <v>293</v>
-      </c>
-      <c r="F4" s="125" t="s">
-        <v>294</v>
-      </c>
-      <c r="G4" s="125" t="s">
-        <v>295</v>
-      </c>
-      <c r="H4" s="125" t="s">
-        <v>296</v>
+      <c r="A4" s="380"/>
+      <c r="B4" s="129" t="s">
+        <v>273</v>
+      </c>
+      <c r="C4" s="127"/>
+      <c r="D4" s="128" t="s">
+        <v>312</v>
+      </c>
+      <c r="E4" s="128" t="s">
+        <v>313</v>
+      </c>
+      <c r="F4" s="128" t="s">
+        <v>314</v>
+      </c>
+      <c r="G4" s="128" t="s">
+        <v>315</v>
+      </c>
+      <c r="H4" s="128" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="49.5">
-      <c r="A5" s="369"/>
+      <c r="A5" s="381"/>
       <c r="B5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="2"/>
       <c r="E5" s="8" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:9" ht="49.5">
-      <c r="A6" s="369"/>
+      <c r="A6" s="381"/>
       <c r="B6" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F6" s="10"/>
     </row>
     <row r="7" spans="1:9" ht="66">
-      <c r="A7" s="369"/>
+      <c r="A7" s="381"/>
       <c r="B7" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="8" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="66">
-      <c r="A8" s="369"/>
+      <c r="A8" s="381"/>
       <c r="B8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="371"/>
+      <c r="C8" s="383"/>
       <c r="D8" s="8" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="66">
-      <c r="A9" s="369"/>
+      <c r="A9" s="381"/>
       <c r="B9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="372"/>
+      <c r="C9" s="384"/>
       <c r="D9" s="8" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F9" s="11"/>
     </row>
     <row r="10" spans="1:9" ht="66">
-      <c r="A10" s="369"/>
+      <c r="A10" s="381"/>
       <c r="B10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="372"/>
+      <c r="C10" s="384"/>
       <c r="D10" s="8" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="66">
-      <c r="A11" s="369"/>
+      <c r="A11" s="381"/>
       <c r="B11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="372"/>
+      <c r="C11" s="384"/>
       <c r="D11" s="8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="66">
-      <c r="A12" s="369"/>
+      <c r="A12" s="381"/>
       <c r="B12" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="373"/>
+      <c r="C12" s="385"/>
       <c r="D12" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="74.25" customHeight="1">
+      <c r="A13" s="381"/>
+      <c r="B13" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="74.25" customHeight="1">
-      <c r="A13" s="369"/>
-      <c r="B13" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="C13" s="13"/>
       <c r="E13" s="8" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="66">
-      <c r="A14" s="369"/>
+      <c r="A14" s="381"/>
       <c r="B14" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="2"/>
       <c r="E14" s="8" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="66">
-      <c r="A15" s="369"/>
+      <c r="A15" s="381"/>
       <c r="B15" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="15"/>
       <c r="E15" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="57" customHeight="1">
-      <c r="A16" s="370"/>
+      <c r="A16" s="382"/>
       <c r="B16" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C16" s="16"/>
       <c r="D16" s="17"/>
       <c r="E16" s="17" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F16" s="18"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="374" t="s">
-        <v>196</v>
-      </c>
-      <c r="B17" s="375"/>
-      <c r="C17" s="375"/>
-      <c r="D17" s="375"/>
-      <c r="E17" s="375"/>
-      <c r="F17" s="376"/>
+      <c r="A17" s="386" t="s">
+        <v>193</v>
+      </c>
+      <c r="B17" s="387"/>
+      <c r="C17" s="387"/>
+      <c r="D17" s="387"/>
+      <c r="E17" s="387"/>
+      <c r="F17" s="388"/>
     </row>
     <row r="18" spans="1:6" ht="18" customHeight="1">
-      <c r="A18" s="367" t="s">
-        <v>196</v>
+      <c r="A18" s="379" t="s">
+        <v>193</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="49.5">
-      <c r="A19" s="369"/>
+      <c r="A19" s="381"/>
       <c r="B19" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="1"/>
       <c r="E19" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F19" s="19"/>
     </row>
     <row r="20" spans="1:6" ht="49.5">
-      <c r="A20" s="369"/>
+      <c r="A20" s="381"/>
       <c r="B20" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="378"/>
+      <c r="C20" s="390"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F20" s="10"/>
     </row>
     <row r="21" spans="1:6" ht="66">
-      <c r="A21" s="369"/>
+      <c r="A21" s="381"/>
       <c r="B21" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="372"/>
+      <c r="C21" s="384"/>
       <c r="D21" s="8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="66">
-      <c r="A22" s="369"/>
+      <c r="A22" s="381"/>
       <c r="B22" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="372"/>
+      <c r="C22" s="384"/>
       <c r="D22" s="8" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="66">
-      <c r="A23" s="369"/>
+      <c r="A23" s="381"/>
       <c r="B23" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="373"/>
+      <c r="C23" s="385"/>
       <c r="D23" s="8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="66">
-      <c r="A24" s="369"/>
+      <c r="A24" s="381"/>
       <c r="B24" s="7" t="s">
         <v>32</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="78">
-      <c r="A25" s="377"/>
+      <c r="A25" s="389"/>
       <c r="B25" s="7" t="s">
         <v>35</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="20" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="78">
@@ -36409,27 +36441,27 @@
       </c>
       <c r="C26" s="22"/>
       <c r="D26" s="23" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F26" s="24"/>
     </row>
-    <row r="27" spans="1:6" ht="78.75" thickBot="1">
+    <row r="27" spans="1:6" ht="78">
       <c r="A27" s="25"/>
       <c r="B27" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C27" s="26"/>
       <c r="D27" s="27" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1"/>
